--- a/dps_config.xlsx
+++ b/dps_config.xlsx
@@ -1,36 +1,38 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Input" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Output" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Sections" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Headings" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Text Deletions" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Cross References" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Tables" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Classification" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Profiling Flags" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Thresholds" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="Priority Scoring" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="Search Terms" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="Control Extraction" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="Pipeline" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="Metadata" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="Docx2md" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Input" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Output" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sections" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Headings" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Text Deletions" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cross References" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tables" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Classification" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Profiling Flags" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Thresholds" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Priority Scoring" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Search Terms" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Control Extraction" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pipeline" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Docx2md" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Docx2jsonl" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acronym Finder" sheetId="19" state="visible" r:id="rId19"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Input'!$A$1:$C$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Output'!$A$1:$C$35</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Output'!$A$1:$C$42</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Sections'!$A$1:$C$37</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Headings'!$A$1:$C$43</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Text Deletions'!$A$1:$C$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Text Deletions'!$A$1:$C$16</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Cross References'!$A$1:$C$38</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Tables'!$A$1:$C$41</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Classification'!$A$1:$C$16</definedName>
@@ -38,10 +40,12 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Thresholds'!$A$1:$C$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Priority Scoring'!$A$1:$C$16</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'Search Terms'!$A$1:$C$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'Control Extraction'!$A$1:$C$52</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'Pipeline'!$A$1:$E$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'Control Extraction'!$A$1:$C$57</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'Pipeline'!$A$1:$E$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="15" hidden="1">'Metadata'!$A$1:$E$32</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="16" hidden="1">'Docx2md'!$A$1:$C$26</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="16" hidden="1">'Docx2md'!$A$1:$C$36</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'Docx2jsonl'!$A$1:$C$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="18" hidden="1">'Acronym Finder'!$A$1:$C$24</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -514,7 +518,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A26"/>
+  <dimension ref="A1:A29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="80" customWidth="1" min="1" max="1"/>
@@ -613,71 +617,92 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Step 1  extract_controls.py        — Pull structured control data</t>
+          <t xml:space="preserve">  Step 1  acronym_finder.py          — Scan for acronym candidates, generates an acronym audit workbook for human review and finalization. The confirmed set of acronyms are then fed into the metadata tagging stage</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Step 2  cross_reference_extractor.py — Capture cross-refs</t>
+          <t xml:space="preserve">  Step 2  extract_controls.py        — Pull structured controls from docx into an excel using regex and heuristics</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Step 3  heading_style_fixer.py     — Fix fake headings</t>
+          <t xml:space="preserve">  Step 3  cross_reference_extractor.py — Capture cross-refs. This includes 'refer to section', URLs in documents, and internal document links to headings</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Step 4  section_splitter.py        — Split docs at H1 boundaries</t>
+          <t xml:space="preserve">  Step 4  heading_style_fixer.py     — Fix false headings (Text that is bold and appears to be heading but is not a heading format for .docx)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Step 5  add_metadata.py            — Stamp sub-docs with metadata</t>
+          <t xml:space="preserve">  Step 5  section_splitter.py        — Split docs at H1 boundaries after the desired char limit</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Step 6  validate_controls.py       — Validate controls in splits</t>
+          <t xml:space="preserve">  Step 6  add_metadata.py            — Stamp sub-docs with metadata</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr"/>
+      <c r="A22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Step 7  docx2md.py                 — Convert word documents to Markdown</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>HOW TO RUN:</t>
+          <t xml:space="preserve">  Step 8  docx2jsonl.py              — Convert word documents to JSONL</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Full pipeline:  python run_pipeline.py</t>
+          <t xml:space="preserve">  Step 9  validate_controls.py       — Validate controls in split versions of docs</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Single step:    python run_pipeline.py --step 0</t>
-        </is>
-      </c>
+      <c r="A25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
+        <is>
+          <t>HOW TO RUN:</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Full pipeline:  python run_pipeline.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Single step:    python run_pipeline.py --step 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
         <is>
           <t xml:space="preserve">  Range:          python run_pipeline.py --step 1-3</t>
         </is>
@@ -1352,7 +1377,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C52"/>
+  <dimension ref="A1:C57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="65" customWidth="1" min="1" max="1"/>
@@ -1404,7 +1429,7 @@
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>enable_checkpoint</t>
+          <t>bold_fallback_if_zero</t>
         </is>
       </c>
       <c r="B4" s="5" t="b">
@@ -1412,166 +1437,196 @@
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>Save progress so re-runs skip already-processed files. Delete checkpoint.json to force fresh run</t>
+          <t>If bold-only extraction finds 0 controls in a doc, auto-retry without the bold requirement</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
+          <t>tables_ignore_bold</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>Always extract control IDs from table cells regardless of bold setting</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>control_id_anchor_start</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>Only match control IDs near the start of a paragraph (filters out inline references)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>control_id_start_chars</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>How many chars from paragraph start to search when anchor_start is enabled</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>min_control_block_lines</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>Discard control blocks with fewer than N content lines. 0 = keep all. 2 = drop inline refs</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>enable_checkpoint</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>Save progress so re-runs skip already-processed files. Delete checkpoint.json to force fresh run</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
           <t>output_format</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B10" s="5" t="inlineStr">
         <is>
           <t>both</t>
         </is>
       </c>
-      <c r="C5" s="6" t="inlineStr">
+      <c r="C10" s="6" t="inlineStr">
         <is>
           <t>"csv", "xlsx", or "both" — controls the output file format for extracted controls</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
         <is>
           <t># Control ID Patterns (Regex)</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr"/>
-      <c r="C6" s="3" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="6" t="inlineStr">
+      <c r="B11" s="3" t="inlineStr"/>
+      <c r="C11" s="3" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
         <is>
           <t>## Regex patterns to match control IDs in document text. One pattern per row.</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="inlineStr"/>
-      <c r="C7" s="5" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t>## Examples matched: AC-1.001, IR001.002, CFG.1.0042, AUP 1.001</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="inlineStr"/>
-      <c r="C8" s="5" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="6" t="inlineStr">
-        <is>
-          <t>## If zero controls extracted, your IDs use a different format — add a pattern here.</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="inlineStr"/>
-      <c r="C9" s="5" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="6" t="inlineStr">
-        <is>
-          <t>## Test patterns at regex101.com before adding.</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="inlineStr"/>
-      <c r="C10" s="5" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>\b[A-Z]{2,4}[-.]?\d{1,3}[-.]\d{2,4}\b</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="inlineStr"/>
-      <c r="C11" s="5" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>\b[A-Z]{2,4}\s+\d{1,3}\.\d{2,4}\b</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr"/>
       <c r="C12" s="5" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>\b[A-Z]{2,4}\d{2,3}\.\d{2,4}\b</t>
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>## Examples matched: AC-1.001, IR001.002, CFG.1.0042, AUP 1.001</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr"/>
       <c r="C13" s="5" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t># Whitelist / Blacklist</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="inlineStr"/>
-      <c r="C14" s="3" t="inlineStr"/>
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>## If zero controls extracted, your IDs use a different format — add a pattern here.</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr"/>
+      <c r="C14" s="5" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>## One control ID per row. Type = "whitelist" or "blacklist".</t>
+          <t>## Test patterns at regex101.com before adding.</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr"/>
       <c r="C15" s="5" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="6" t="inlineStr">
-        <is>
-          <t>## Whitelist: if ANY whitelist entries exist, ONLY matching controls are kept.</t>
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>\b[A-Z]{2,4}[-.]?\d{1,3}[-.]\d{2,4}\b</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr"/>
       <c r="C16" s="5" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="6" t="inlineStr">
-        <is>
-          <t>## Blacklist: matching controls are excluded (applied after whitelist).</t>
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>\b[A-Z]{2,4}\s+\d{1,3}\.\d{2,4}\b</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr"/>
       <c r="C17" s="5" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="6" t="inlineStr">
-        <is>
-          <t>## Supports exact IDs (e.g. AC-1.001) and prefix wildcards (e.g. AC-*).</t>
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>\b[A-Z]{2,4}\d{2,3}\.\d{2,4}\b</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr"/>
       <c r="C18" s="5" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="6" t="inlineStr">
-        <is>
-          <t>## Add as many rows as needed. Leave this section empty to keep all controls.</t>
-        </is>
-      </c>
-      <c r="B19" s="5" t="inlineStr"/>
-      <c r="C19" s="5" t="inlineStr"/>
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t># Whitelist / Blacklist</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr"/>
+      <c r="C19" s="3" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t># Guidance Keywords</t>
-        </is>
-      </c>
-      <c r="B20" s="3" t="inlineStr"/>
-      <c r="C20" s="3" t="inlineStr"/>
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>## One control ID per row. Type = "whitelist" or "blacklist".</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr"/>
+      <c r="C20" s="5" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>## Keywords marking the boundary between control description and supplemental guidance.</t>
+          <t>## Whitelist: if ANY whitelist entries exist, ONLY matching controls are kept.</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr"/>
@@ -1580,88 +1635,88 @@
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>## One keyword per row. When a paragraph contains one of these, text after it is classified as guidance.</t>
+          <t>## Blacklist: matching controls are excluded (applied after whitelist).</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr"/>
       <c r="C22" s="5" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="5" t="inlineStr">
-        <is>
-          <t>implementation guidance</t>
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>## Supports exact IDs (e.g. AC-1.001) and prefix wildcards (e.g. AC-*).</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr"/>
       <c r="C23" s="5" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="5" t="inlineStr">
-        <is>
-          <t>implementation:</t>
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>## Add as many rows as needed. Leave this section empty to keep all controls.</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr"/>
       <c r="C24" s="5" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>guidelines:</t>
-        </is>
-      </c>
-      <c r="B25" s="5" t="inlineStr"/>
-      <c r="C25" s="5" t="inlineStr"/>
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t># Guidance Keywords</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr"/>
+      <c r="C25" s="3" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="5" t="inlineStr">
-        <is>
-          <t>how to implement</t>
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>## Keywords marking the boundary between control description and supplemental guidance.</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr"/>
       <c r="C26" s="5" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="5" t="inlineStr">
-        <is>
-          <t>supplemental guidance</t>
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>## One keyword per row. When a paragraph contains one of these, text after it is classified as guidance.</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr"/>
       <c r="C27" s="5" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="inlineStr">
-        <is>
-          <t># Metadata Triggers</t>
-        </is>
-      </c>
-      <c r="B28" s="3" t="inlineStr"/>
-      <c r="C28" s="3" t="inlineStr"/>
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>implementation guidance</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr"/>
+      <c r="C28" s="5" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="6" t="inlineStr">
-        <is>
-          <t>## Category | Keyword — triggers for extracting document-level metadata (purpose, scope, applicability).</t>
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>implementation:</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr"/>
       <c r="C29" s="5" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="6" t="inlineStr">
-        <is>
-          <t>## Column A = category name, Column B = keyword. Multiple keywords per category are allowed (one per row).</t>
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>guidelines:</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr"/>
       <c r="C30" s="5" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="6" t="inlineStr">
-        <is>
-          <t>## The extractor scans the first N paragraphs (see metadata_scan_paragraphs) for these keywords.</t>
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>how to implement</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr"/>
@@ -1670,77 +1725,57 @@
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>purpose</t>
-        </is>
-      </c>
-      <c r="B32" s="5" t="inlineStr">
-        <is>
-          <t>purpose</t>
-        </is>
-      </c>
+          <t>supplemental guidance</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr"/>
       <c r="C32" s="5" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="5" t="inlineStr">
-        <is>
-          <t>purpose</t>
-        </is>
-      </c>
-      <c r="B33" s="5" t="inlineStr">
-        <is>
-          <t>objective</t>
-        </is>
-      </c>
-      <c r="C33" s="5" t="inlineStr"/>
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t># Metadata Triggers</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr"/>
+      <c r="C33" s="3" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="5" t="inlineStr">
-        <is>
-          <t>purpose</t>
-        </is>
-      </c>
-      <c r="B34" s="5" t="inlineStr">
-        <is>
-          <t>intent</t>
-        </is>
-      </c>
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>## Category | Keyword — triggers for extracting document-level metadata (purpose, scope, applicability).</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr"/>
       <c r="C34" s="5" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="5" t="inlineStr">
-        <is>
-          <t>scope</t>
-        </is>
-      </c>
-      <c r="B35" s="5" t="inlineStr">
-        <is>
-          <t>scope</t>
-        </is>
-      </c>
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>## Column A = category name, Column B = keyword. Multiple keywords per category are allowed (one per row).</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr"/>
       <c r="C35" s="5" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="5" t="inlineStr">
-        <is>
-          <t>scope</t>
-        </is>
-      </c>
-      <c r="B36" s="5" t="inlineStr">
-        <is>
-          <t>coverage</t>
-        </is>
-      </c>
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t>## The extractor scans the first N paragraphs (see metadata_scan_paragraphs) for these keywords.</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="inlineStr"/>
       <c r="C36" s="5" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>scope</t>
+          <t>purpose</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>boundary</t>
+          <t>purpose</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr"/>
@@ -1748,12 +1783,12 @@
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>applicability</t>
+          <t>purpose</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>applicability</t>
+          <t>objective</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr"/>
@@ -1761,12 +1796,12 @@
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>applicability</t>
+          <t>purpose</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>applies to</t>
+          <t>intent</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr"/>
@@ -1774,209 +1809,283 @@
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>applicability</t>
+          <t>scope</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>applies for</t>
+          <t>scope</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="3" t="inlineStr">
-        <is>
-          <t># Heading Detection (Advanced)</t>
-        </is>
-      </c>
-      <c r="B41" s="3" t="inlineStr"/>
-      <c r="C41" s="3" t="inlineStr"/>
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>scope</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>coverage</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>heading_detection.use_word_heading_style</t>
-        </is>
-      </c>
-      <c r="B42" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="C42" s="6" t="inlineStr">
-        <is>
-          <t>Use Word heading styles for detection</t>
-        </is>
-      </c>
+          <t>scope</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>boundary</t>
+        </is>
+      </c>
+      <c r="C42" s="5" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>heading_detection.section_keyword_pattern</t>
+          <t>applicability</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>^[Ss]ection\s+\d{1,2}</t>
-        </is>
-      </c>
-      <c r="C43" s="6" t="inlineStr">
-        <is>
-          <t>Regex for section headings like "Section 4"</t>
-        </is>
-      </c>
+          <t>applicability</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>heading_detection.numbered_title_pattern</t>
+          <t>applicability</t>
         </is>
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>^\d{1,2}\.?\d{0,2}\s+[A-Z][a-zA-Z\s]{3,50}$</t>
-        </is>
-      </c>
-      <c r="C44" s="6" t="inlineStr">
-        <is>
-          <t>Regex for numbered titles like "4.1 Access Control"</t>
-        </is>
-      </c>
+          <t>applies to</t>
+        </is>
+      </c>
+      <c r="C44" s="5" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>heading_detection.detect_allcaps</t>
-        </is>
-      </c>
-      <c r="B45" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="C45" s="6" t="inlineStr">
-        <is>
-          <t>Detect ALL CAPS headings</t>
-        </is>
-      </c>
+          <t>applicability</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>applies for</t>
+        </is>
+      </c>
+      <c r="C45" s="5" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="5" t="inlineStr">
-        <is>
-          <t>heading_detection.allcaps_max_length</t>
-        </is>
-      </c>
-      <c r="B46" s="5" t="n">
-        <v>80</v>
-      </c>
-      <c r="C46" s="6" t="inlineStr">
-        <is>
-          <t>Max chars for all-caps heading</t>
-        </is>
-      </c>
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t># Heading Detection (Advanced)</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr"/>
+      <c r="C46" s="3" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>heading_detection.allcaps_min_words</t>
-        </is>
-      </c>
-      <c r="B47" s="5" t="n">
-        <v>3</v>
+          <t>heading_detection.use_word_heading_style</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="b">
+        <v>1</v>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>Min words for all-caps heading</t>
+          <t>Use Word heading styles for detection</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>heading_detection.detect_bold_short</t>
-        </is>
-      </c>
-      <c r="B48" s="5" t="b">
-        <v>1</v>
+          <t>heading_detection.section_keyword_pattern</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="inlineStr">
+        <is>
+          <t>^[Ss]ection\s+\d{1,2}</t>
+        </is>
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>Detect short bold text as headings</t>
+          <t>Regex for section headings like "Section 4"</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>heading_detection.bold_max_length</t>
-        </is>
-      </c>
-      <c r="B49" s="5" t="n">
-        <v>60</v>
+          <t>heading_detection.numbered_title_pattern</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="inlineStr">
+        <is>
+          <t>^\d{1,2}\.?\d{0,2}\s+[A-Z][a-zA-Z\s]{3,50}$</t>
+        </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>Max chars for bold heading</t>
+          <t>Regex for numbered titles like "4.1 Access Control"</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="3" t="inlineStr">
-        <is>
-          <t># Implementation Trigger (Regex)</t>
-        </is>
-      </c>
-      <c r="B50" s="3" t="inlineStr"/>
-      <c r="C50" s="3" t="inlineStr"/>
+      <c r="A50" s="5" t="inlineStr">
+        <is>
+          <t>heading_detection.detect_allcaps</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="C50" s="6" t="inlineStr">
+        <is>
+          <t>Detect ALL CAPS headings</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>implementation_trigger</t>
-        </is>
-      </c>
-      <c r="B51" s="5" t="inlineStr">
-        <is>
-          <t>(?i)(implementation guidance|implementation:|guidelines:|how to implement|supplemental guidance)</t>
-        </is>
+          <t>heading_detection.allcaps_max_length</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="n">
+        <v>80</v>
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>Regex for guidance boundary within a control block</t>
+          <t>Max chars for all-caps heading</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
         <is>
+          <t>heading_detection.allcaps_min_words</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="C52" s="6" t="inlineStr">
+        <is>
+          <t>Min words for all-caps heading</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="5" t="inlineStr">
+        <is>
+          <t>heading_detection.detect_bold_short</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="C53" s="6" t="inlineStr">
+        <is>
+          <t>Detect short bold text as headings</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="5" t="inlineStr">
+        <is>
+          <t>heading_detection.bold_max_length</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="n">
+        <v>60</v>
+      </c>
+      <c r="C54" s="6" t="inlineStr">
+        <is>
+          <t>Max chars for bold heading</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="inlineStr">
+        <is>
+          <t># Implementation Trigger (Regex)</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="inlineStr"/>
+      <c r="C55" s="3" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="5" t="inlineStr">
+        <is>
+          <t>implementation_trigger</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="inlineStr">
+        <is>
+          <t>(?i)(implementation guidance|implementation:|guidelines:|how to implement|supplemental guidance)</t>
+        </is>
+      </c>
+      <c r="C56" s="6" t="inlineStr">
+        <is>
+          <t>Regex for guidance boundary within a control block</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="5" t="inlineStr">
+        <is>
           <t>metadata_scan_paragraphs</t>
         </is>
       </c>
-      <c r="B52" s="5" t="n">
+      <c r="B57" s="5" t="n">
         <v>40</v>
       </c>
-      <c r="C52" s="6" t="inlineStr">
+      <c r="C57" s="6" t="inlineStr">
         <is>
           <t>How many paragraphs from top of doc to scan for metadata</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C52"/>
-  <dataValidations count="6">
+  <autoFilter ref="A1:C57"/>
+  <dataValidations count="9">
     <dataValidation sqref="B3" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid value" error="Please select TRUE or FALSE" type="list">
       <formula1>"TRUE,FALSE"</formula1>
     </dataValidation>
     <dataValidation sqref="B4" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid value" error="Please select TRUE or FALSE" type="list">
       <formula1>"TRUE,FALSE"</formula1>
     </dataValidation>
-    <dataValidation sqref="B5" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="Invalid value" error="Please select one of: csv, xlsx, both" type="list">
+    <dataValidation sqref="B5" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid value" error="Please select TRUE or FALSE" type="list">
+      <formula1>"TRUE,FALSE"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B6" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid value" error="Please select TRUE or FALSE" type="list">
+      <formula1>"TRUE,FALSE"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B9" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid value" error="Please select TRUE or FALSE" type="list">
+      <formula1>"TRUE,FALSE"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B10" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="Invalid value" error="Please select one of: csv, xlsx, both" type="list">
       <formula1>"csv,xlsx,both"</formula1>
     </dataValidation>
-    <dataValidation sqref="B42" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid value" error="Please select TRUE or FALSE" type="list">
+    <dataValidation sqref="B47" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid value" error="Please select TRUE or FALSE" type="list">
       <formula1>"TRUE,FALSE"</formula1>
     </dataValidation>
-    <dataValidation sqref="B45" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid value" error="Please select TRUE or FALSE" type="list">
+    <dataValidation sqref="B50" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid value" error="Please select TRUE or FALSE" type="list">
       <formula1>"TRUE,FALSE"</formula1>
     </dataValidation>
-    <dataValidation sqref="B48" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid value" error="Please select TRUE or FALSE" type="list">
+    <dataValidation sqref="B53" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid value" error="Please select TRUE or FALSE" type="list">
       <formula1>"TRUE,FALSE"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1990,7 +2099,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2056,12 +2165,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Step 1 - Control Extractor</t>
+          <t>Step 1 - Acronym Finder</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>extract_controls.py</t>
+          <t>acronym_finder.py</t>
         </is>
       </c>
       <c r="D3" t="b">
@@ -2069,7 +2178,7 @@
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
-          <t>Extract structured control data from compliance docs</t>
+          <t>Scan all docs for acronym candidates and generate audit Excel</t>
         </is>
       </c>
     </row>
@@ -2079,12 +2188,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Step 2 - Cross-Reference Extractor</t>
+          <t>Step 2 - Control Extractor</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>cross_reference_extractor.py</t>
+          <t>extract_controls.py</t>
         </is>
       </c>
       <c r="D4" t="b">
@@ -2092,7 +2201,7 @@
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>Capture all cross-refs BEFORE any structural changes</t>
+          <t>Extract structured control data from compliance docs</t>
         </is>
       </c>
     </row>
@@ -2102,12 +2211,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Step 3 - Heading Style Fixer</t>
+          <t>Step 3 - Cross-Reference Extractor</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>heading_style_fixer.py</t>
+          <t>cross_reference_extractor.py</t>
         </is>
       </c>
       <c r="D5" t="b">
@@ -2115,7 +2224,7 @@
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>Convert fake bold headings to real Word Heading styles</t>
+          <t>Capture all cross-refs BEFORE any structural changes</t>
         </is>
       </c>
     </row>
@@ -2125,12 +2234,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Step 4 - Section Splitter</t>
+          <t>Step 4 - Heading Style Fixer</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>section_splitter.py</t>
+          <t>heading_style_fixer.py</t>
         </is>
       </c>
       <c r="D6" t="b">
@@ -2138,7 +2247,7 @@
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>Split fixed docs at H1 boundaries into sub-documents</t>
+          <t>Convert fake bold headings to real Word Heading styles</t>
         </is>
       </c>
     </row>
@@ -2148,12 +2257,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Step 5 - Metadata Injector</t>
+          <t>Step 5 - Section Splitter</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>add_metadata.py</t>
+          <t>section_splitter.py</t>
         </is>
       </c>
       <c r="D7" t="b">
@@ -2161,7 +2270,7 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>Add identity metadata (name, URL, scope, intent, tags) to sub-documents</t>
+          <t>Split fixed docs at H1 boundaries into sub-documents</t>
         </is>
       </c>
     </row>
@@ -2171,12 +2280,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Step 6 - Control Validator</t>
+          <t>Step 6 - Metadata Injector</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>validate_controls.py</t>
+          <t>add_metadata.py</t>
         </is>
       </c>
       <c r="D8" t="b">
@@ -2184,14 +2293,83 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>Validate all Step 1 controls are present in Step 4 split documents</t>
+          <t>Add identity metadata to sub-documents</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Step 7 - DOCX to Markdown</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>docx2md.py</t>
+        </is>
+      </c>
+      <c r="D9" t="b">
+        <v>1</v>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>Convert .docx files to clean Markdown with YAML frontmatter</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Step 8 - DOCX to JSONL</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>docx2jsonl.py</t>
+        </is>
+      </c>
+      <c r="D10" t="b">
+        <v>1</v>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>Convert .docx files to chunked JSONL for RAG/vector DB ingestion</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Step 9 - Control Validator</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>validate_controls.py</t>
+        </is>
+      </c>
+      <c r="D11" t="b">
+        <v>1</v>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>Validate all Step 2 controls are present in Step 5 split documents</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E8"/>
+  <autoFilter ref="A1:E11"/>
   <dataValidations count="1">
-    <dataValidation sqref="D2:D8" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid value" error="Please select TRUE or FALSE" type="list">
+    <dataValidation sqref="D2:D11" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid value" error="Please select TRUE or FALSE" type="list">
       <formula1>"TRUE,FALSE"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2681,12 +2859,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C26"/>
+  <dimension ref="A1:C36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="47" customWidth="1" min="1" max="1"/>
     <col width="44" customWidth="1" min="2" max="2"/>
-    <col width="54" customWidth="1" min="3" max="3"/>
+    <col width="65" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2709,349 +2887,1026 @@
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t># Output</t>
+          <t># Input Mode</t>
         </is>
       </c>
       <c r="B2" s="4" t="inlineStr"/>
-      <c r="C2" s="4" t="inlineStr"/>
+      <c r="C2" s="3" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>pure_conversion</t>
+        </is>
+      </c>
+      <c r="B3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>TRUE = Pure Conversion (read from input/), FALSE = Optimized (read from step output)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>optimized_source_step</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>heading_fixes</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>Step output to read when not pure: "heading_fixes", "split_documents", "metadata"</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t># Output</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr"/>
+      <c r="C5" s="3" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>output_directory</t>
         </is>
       </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>./output/7 - markdown</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>Where converted .md files are written</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t># Image Handling</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr"/>
+      <c r="C7" s="3" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>image_handling</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>extract</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>"extract", "placeholder", or "skip"</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>image_subfolder</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>images</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>Subfolder name under each doc's image dir</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t># Table Conversion</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr"/>
+      <c r="C10" s="3" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>table_strategy</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>"auto" (recommended), "markdown", or "html"</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t># Heading &amp; Text Cleanup</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr"/>
+      <c r="C12" s="3" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>heading_normalization</t>
+        </is>
+      </c>
+      <c r="B13" t="b">
+        <v>1</v>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>Shift heading levels so doc starts at H1</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>max_heading_level</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>2</v>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>Max heading depth in output (2 = only H1/H2). H3+ collapsed to this level.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>max_consecutive_blank_lines</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>2</v>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>Collapse runs of blank lines</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>clean_smart_quotes</t>
+        </is>
+      </c>
+      <c r="B16" t="b">
+        <v>1</v>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>Convert smart quotes to ASCII</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>strip_zero_width_chars</t>
+        </is>
+      </c>
+      <c r="B17" t="b">
+        <v>1</v>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>Remove zero-width spaces, BOM, etc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>extract_text_boxes</t>
+        </is>
+      </c>
+      <c r="B18" t="b">
+        <v>1</v>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>Extract floating text box content inline</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t># Doc URL Resolution</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr"/>
+      <c r="C19" s="3" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>include_doc_url</t>
+        </is>
+      </c>
+      <c r="B20" t="b">
+        <v>1</v>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>Resolve Doc URLs from metadata.url Excel lookup into frontmatter</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t># Metadata Placement</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr"/>
+      <c r="C21" s="3" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>metadata_placement</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>top</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>"top" = YAML frontmatter only; "top_and_bottom" = also append readable block at end</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t># Control ID Headings</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr"/>
+      <c r="C23" s="3" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>promote_control_ids_to_heading</t>
+        </is>
+      </c>
+      <c r="B24" t="b">
+        <v>1</v>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>Promote paragraphs with control IDs to H2 headings (uses control_extraction patterns)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t># Logging</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr"/>
+      <c r="C25" s="3" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>log_file_prefix</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>docx2md_log</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>Prefix for timestamped log Excel file</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t># Metadata Frontmatter</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr"/>
+      <c r="C27" s="3" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>include_metadata_frontmatter</t>
+        </is>
+      </c>
+      <c r="B28" t="b">
+        <v>1</v>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>Add YAML frontmatter block at top of each .md file</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="7" t="inlineStr">
+        <is>
+          <t>## Metadata fields: Name | Source | Default</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr"/>
+      <c r="C29" s="5" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>core:title</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>source_file</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>filename</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>author</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>core:author</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>created</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>core:created</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>core:modified</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>doc_id</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>filename_regex:([A-Z]+-[A-Z]+-\d{4}-\d+)</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>converted</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>converted_date</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:C36"/>
+  <dataValidations count="11">
+    <dataValidation sqref="B3" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid value" error="Please select TRUE or FALSE" type="list">
+      <formula1>"TRUE,FALSE"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B8" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="Invalid value" error="Please select one of: extract, placeholder, skip" type="list">
+      <formula1>"extract,placeholder,skip"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B11" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="Invalid value" error="Please select one of: auto, markdown, html" type="list">
+      <formula1>"auto,markdown,html"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B13" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid value" error="Please select TRUE or FALSE" type="list">
+      <formula1>"TRUE,FALSE"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B16" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid value" error="Please select TRUE or FALSE" type="list">
+      <formula1>"TRUE,FALSE"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B17" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid value" error="Please select TRUE or FALSE" type="list">
+      <formula1>"TRUE,FALSE"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B18" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid value" error="Please select TRUE or FALSE" type="list">
+      <formula1>"TRUE,FALSE"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B20" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid value" error="Please select TRUE or FALSE" type="list">
+      <formula1>"TRUE,FALSE"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B22" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="Invalid value" error="Please select one of: top, top_and_bottom" type="list">
+      <formula1>"top,top_and_bottom"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B24" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid value" error="Please select TRUE or FALSE" type="list">
+      <formula1>"TRUE,FALSE"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B28" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid value" error="Please select TRUE or FALSE" type="list">
+      <formula1>"TRUE,FALSE"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="36" customWidth="1" min="2" max="2"/>
+    <col width="65" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t># Input Mode</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr"/>
+      <c r="C2" s="3" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>pure_conversion</t>
+        </is>
+      </c>
+      <c r="B3" t="b">
+        <v>0</v>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>TRUE = Pure Conversion (read from input/), FALSE = Optimized (read from step output)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>optimized_source_step</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>heading_fixes</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>Step output to read when not pure: "heading_fixes", "split_documents", "metadata"</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t># Output</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr"/>
+      <c r="C5" s="3" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>output_directory</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>./output/8 - jsonl</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>Where converted .jsonl.txt files are written</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t># Chunking</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr"/>
+      <c r="C7" s="3" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>max_chunk_chars</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1500</v>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>Maximum characters per chunk</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>overlap_words</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>30</v>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>Words to overlap between consecutive chunks</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>min_chunk_chars</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>100</v>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>Merge trailing chunks smaller than this into previous</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t># Acronym Definitions</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr"/>
+      <c r="C11" s="3" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>acronym_definitions_file</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>./input/Acronym_Definitions.xlsx</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>Path to confirmed acronym definitions Excel (Per Document sheet)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t># Tag Mapping</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr"/>
+      <c r="C13" s="3" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>tag_file</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>Optional Excel file mapping documents to tags (leave empty to skip)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:C14"/>
+  <dataValidations count="1">
+    <dataValidation sqref="B3" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid value" error="Please select TRUE or FALSE" type="list">
+      <formula1>"TRUE,FALSE"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="52" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="65" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t># Output</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr"/>
+      <c r="C2" s="3" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>output_file</t>
+        </is>
+      </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>./output/markdown</t>
-        </is>
-      </c>
-      <c r="C3" s="7" t="inlineStr">
-        <is>
-          <t>Where converted .md files are written</t>
+          <t>acronym_audit.xlsx</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>Filename for the audit Excel report</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t># Image Handling</t>
+          <t># Search Settings</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr"/>
-      <c r="C4" s="4" t="inlineStr"/>
+      <c r="C4" s="3" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>image_handling</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>extract</t>
-        </is>
-      </c>
-      <c r="C5" s="7" t="inlineStr">
-        <is>
-          <t>"extract", "placeholder", or "skip"</t>
+          <t>search.min_length</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>Minimum acronym length (2 = 'AC')</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>image_subfolder</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>images</t>
-        </is>
-      </c>
-      <c r="C6" s="7" t="inlineStr">
-        <is>
-          <t>Subfolder name under each doc's image dir</t>
+          <t>search.max_length</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>8</v>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>Maximum acronym length</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t># Table Conversion</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr"/>
-      <c r="C7" s="4" t="inlineStr"/>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>search.scan_tables</t>
+        </is>
+      </c>
+      <c r="B7" t="b">
+        <v>1</v>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>Include acronyms found inside tables</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>table_strategy</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>auto</t>
-        </is>
-      </c>
-      <c r="C8" s="7" t="inlineStr">
-        <is>
-          <t>"auto" (recommended), "markdown", or "html"</t>
+          <t>search.scan_headers_footers</t>
+        </is>
+      </c>
+      <c r="B8" t="b">
+        <v>1</v>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>Include acronyms found in headers/footers</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t># Heading &amp; Text Cleanup</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr"/>
-      <c r="C9" s="4" t="inlineStr"/>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>search.scan_textboxes</t>
+        </is>
+      </c>
+      <c r="B9" t="b">
+        <v>1</v>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>Include acronyms found in text boxes</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>heading_normalization</t>
-        </is>
-      </c>
-      <c r="B10" t="b">
+          <t>search.min_global_occurrences</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
         <v>1</v>
       </c>
-      <c r="C10" s="7" t="inlineStr">
-        <is>
-          <t>Shift heading levels so doc starts at H1</t>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>Min occurrences across ALL docs to appear in results</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>max_consecutive_blank_lines</t>
+          <t>search.min_doc_occurrences</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
-      </c>
-      <c r="C11" s="7" t="inlineStr">
-        <is>
-          <t>Collapse runs of blank lines</t>
+        <v>1</v>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>Min occurrences within a single doc to appear</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>clean_smart_quotes</t>
-        </is>
-      </c>
-      <c r="B12" t="b">
-        <v>1</v>
-      </c>
-      <c r="C12" s="7" t="inlineStr">
-        <is>
-          <t>Convert smart quotes to ASCII</t>
-        </is>
-      </c>
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t># Detection Patterns</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr"/>
+      <c r="C12" s="3" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>strip_zero_width_chars</t>
+          <t>patterns.pure_caps</t>
         </is>
       </c>
       <c r="B13" t="b">
         <v>1</v>
       </c>
-      <c r="C13" s="7" t="inlineStr">
-        <is>
-          <t>Remove zero-width spaces, BOM, etc.</t>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>ABC, NIST, GCC</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>extract_text_boxes</t>
+          <t>patterns.caps_with_numbers</t>
         </is>
       </c>
       <c r="B14" t="b">
         <v>1</v>
       </c>
-      <c r="C14" s="7" t="inlineStr">
-        <is>
-          <t>Extract floating text box content inline</t>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>AC-2, 800-53</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t># Logging</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="inlineStr"/>
-      <c r="C15" s="4" t="inlineStr"/>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>patterns.caps_with_hyphens</t>
+        </is>
+      </c>
+      <c r="B15" t="b">
+        <v>1</v>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>FedRAMP, ATO-P</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>log_file_prefix</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>docx2md_log</t>
-        </is>
-      </c>
-      <c r="C16" s="7" t="inlineStr">
-        <is>
-          <t>Prefix for timestamped log Excel file</t>
+          <t>patterns.caps_with_slashes</t>
+        </is>
+      </c>
+      <c r="B16" t="b">
+        <v>1</v>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>IT/OT, CI/CD</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t># Metadata Frontmatter</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="inlineStr"/>
-      <c r="C17" s="4" t="inlineStr"/>
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>patterns.parenthetical_defs</t>
+        </is>
+      </c>
+      <c r="B17" t="b">
+        <v>1</v>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>"Multi-Factor Authentication (MFA)"</t>
+        </is>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>include_metadata_frontmatter</t>
-        </is>
-      </c>
-      <c r="B18" t="b">
-        <v>1</v>
-      </c>
-      <c r="C18" s="7" t="inlineStr">
-        <is>
-          <t>Add YAML frontmatter block at top of each .md file</t>
-        </is>
-      </c>
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t># Ignore List (one per row)</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr"/>
+      <c r="C18" s="3" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="7" t="inlineStr">
         <is>
-          <t>## Metadata fields: Name | Source | Default</t>
+          <t>## Acronyms and uppercase words to skip entirely</t>
         </is>
       </c>
       <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr"/>
+      <c r="C19" s="5" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>title</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>core:title</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr"/>
+      <c r="A20" t="inlineStr"/>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" s="5" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>source_file</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>filename</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr"/>
+      <c r="A21" t="inlineStr"/>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" s="5" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>author</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>core:author</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+      <c r="A22" t="inlineStr"/>
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" s="5" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>created</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>core:created</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr"/>
+      <c r="A23" t="inlineStr"/>
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" s="5" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>modified</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>core:modified</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>doc_id</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>filename_regex:([A-Z]+-[A-Z]+-\d{4}-\d+)</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>converted</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>converted_date</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr"/>
+      <c r="A24" t="inlineStr"/>
+      <c r="B24" t="inlineStr"/>
+      <c r="C24" s="5" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C26"/>
-  <dataValidations count="7">
-    <dataValidation sqref="B5" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="Invalid value" error="Please select one of: extract, placeholder, skip" type="list">
-      <formula1>"extract,placeholder,skip"</formula1>
-    </dataValidation>
-    <dataValidation sqref="B8" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="Invalid value" error="Please select one of: auto, markdown, html" type="list">
-      <formula1>"auto,markdown,html"</formula1>
-    </dataValidation>
-    <dataValidation sqref="B10" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid value" error="Please select TRUE or FALSE" type="list">
+  <autoFilter ref="A1:C24"/>
+  <dataValidations count="8">
+    <dataValidation sqref="B7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid value" error="Please select TRUE or FALSE" type="list">
       <formula1>"TRUE,FALSE"</formula1>
     </dataValidation>
-    <dataValidation sqref="B12" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid value" error="Please select TRUE or FALSE" type="list">
+    <dataValidation sqref="B8" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid value" error="Please select TRUE or FALSE" type="list">
+      <formula1>"TRUE,FALSE"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B9" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid value" error="Please select TRUE or FALSE" type="list">
       <formula1>"TRUE,FALSE"</formula1>
     </dataValidation>
     <dataValidation sqref="B13" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid value" error="Please select TRUE or FALSE" type="list">
@@ -3060,7 +3915,13 @@
     <dataValidation sqref="B14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid value" error="Please select TRUE or FALSE" type="list">
       <formula1>"TRUE,FALSE"</formula1>
     </dataValidation>
-    <dataValidation sqref="B18" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid value" error="Please select TRUE or FALSE" type="list">
+    <dataValidation sqref="B15" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid value" error="Please select TRUE or FALSE" type="list">
+      <formula1>"TRUE,FALSE"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B16" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid value" error="Please select TRUE or FALSE" type="list">
+      <formula1>"TRUE,FALSE"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B17" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid value" error="Please select TRUE or FALSE" type="list">
       <formula1>"TRUE,FALSE"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3257,7 +4118,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C35"/>
+  <dimension ref="A1:C42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
@@ -3422,7 +4283,7 @@
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t># Step 1 — Controls</t>
+          <t># Step 1 — Acronyms</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr"/>
@@ -3431,12 +4292,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>controls.directory</t>
+          <t>acronyms.directory</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>1 - controls</t>
+          <t>1 - acronyms</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
@@ -3448,118 +4309,118 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>controls.output_file</t>
+          <t>acronyms.output_file</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>controls_output.csv</t>
+          <t>acronym_audit.xlsx</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>CSV output</t>
+          <t>Audit Excel output</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>controls.output_file_xlsx</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>controls_output.xlsx</t>
-        </is>
-      </c>
-      <c r="C14" s="7" t="inlineStr">
-        <is>
-          <t>Excel output</t>
-        </is>
-      </c>
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t># Step 2 — Controls</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr"/>
+      <c r="C14" s="4" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>controls.checkpoint_file</t>
+          <t>controls.directory</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>checkpoint.json</t>
+          <t>2 - controls</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>Resume progress tracker</t>
+          <t>Sub-folder name</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>controls.error_log</t>
+          <t>controls.output_file</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>errors.log</t>
+          <t>controls_output.csv</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>Error log file</t>
+          <t>CSV output</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t># Step 2 — Cross References</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="inlineStr"/>
-      <c r="C17" s="4" t="inlineStr"/>
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>controls.output_file_xlsx</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>controls_output.xlsx</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>Excel output</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>cross_references.directory</t>
+          <t>controls.checkpoint_file</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2 - cross_references</t>
+          <t>checkpoint.json</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>Sub-folder name</t>
+          <t>Resume progress tracker</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>cross_references.output_file</t>
+          <t>controls.error_log</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>cross_references.csv</t>
+          <t>errors.log</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>CSV output</t>
+          <t>Error log file</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t># Step 3 — Heading Fixes</t>
+          <t># Step 3 — Cross References</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr"/>
@@ -3568,12 +4429,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>heading_fixes.directory</t>
+          <t>cross_references.directory</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>3 - heading_fixes</t>
+          <t>3 - cross_references</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
@@ -3585,24 +4446,24 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>heading_fixes.changes_file</t>
+          <t>cross_references.output_file</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>heading_changes.csv</t>
+          <t>cross_references.csv</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>Changes log CSV</t>
+          <t>CSV output</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t># Step 4 — Split Documents</t>
+          <t># Step 4 — Heading Fixes</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr"/>
@@ -3611,12 +4472,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>split_documents.directory</t>
+          <t>heading_fixes.directory</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>4 - split_documents</t>
+          <t>4 - heading_fixes</t>
         </is>
       </c>
       <c r="C24" s="7" t="inlineStr">
@@ -3628,24 +4489,24 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>split_documents.manifest_file</t>
+          <t>heading_fixes.changes_file</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>split_manifest.csv</t>
+          <t>heading_changes.csv</t>
         </is>
       </c>
       <c r="C25" s="7" t="inlineStr">
         <is>
-          <t>Split manifest CSV</t>
+          <t>Changes log CSV</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t># Step 5 — Metadata</t>
+          <t># Step 5 — Split Documents</t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr"/>
@@ -3654,12 +4515,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>metadata.directory</t>
+          <t>split_documents.directory</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>5 - metadata</t>
+          <t>5 - split_documents</t>
         </is>
       </c>
       <c r="C27" s="7" t="inlineStr">
@@ -3671,24 +4532,24 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>metadata.manifest_file</t>
+          <t>split_documents.manifest_file</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>metadata_manifest.csv</t>
+          <t>split_manifest.csv</t>
         </is>
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
-          <t>Metadata manifest CSV</t>
+          <t>Split manifest CSV</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t># Step 6 — Validation</t>
+          <t># Step 6 — Metadata</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr"/>
@@ -3697,12 +4558,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>validation.directory</t>
+          <t>metadata.directory</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>6 - validation</t>
+          <t>6 - metadata</t>
         </is>
       </c>
       <c r="C30" s="7" t="inlineStr">
@@ -3714,82 +4575,177 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>validation.output_file</t>
+          <t>metadata.manifest_file</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>control_validation.csv</t>
+          <t>metadata_manifest.csv</t>
         </is>
       </c>
       <c r="C31" s="7" t="inlineStr">
         <is>
-          <t>CSV output</t>
+          <t>Metadata manifest CSV</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>validation.review_file</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>validation_review.xlsx</t>
-        </is>
-      </c>
-      <c r="C32" s="7" t="inlineStr">
-        <is>
-          <t>Human review workbook</t>
-        </is>
-      </c>
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t># Step 7 — Markdown</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr"/>
+      <c r="C32" s="4" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="4" t="inlineStr">
-        <is>
-          <t># Consolidated Report</t>
-        </is>
-      </c>
-      <c r="B33" s="4" t="inlineStr"/>
-      <c r="C33" s="4" t="inlineStr"/>
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>markdown.directory</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>7 - markdown</t>
+        </is>
+      </c>
+      <c r="C33" s="7" t="inlineStr">
+        <is>
+          <t>Sub-folder name</t>
+        </is>
+      </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>consolidated_report.enabled</t>
-        </is>
-      </c>
-      <c r="B34" t="b">
-        <v>1</v>
-      </c>
-      <c r="C34" s="7" t="inlineStr">
-        <is>
-          <t>Build single .xlsx workbook after all steps</t>
-        </is>
-      </c>
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t># Step 8 — JSONL</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr"/>
+      <c r="C34" s="4" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
+          <t>jsonl.directory</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>8 - jsonl</t>
+        </is>
+      </c>
+      <c r="C35" s="7" t="inlineStr">
+        <is>
+          <t>Sub-folder name</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t># Step 9 — Validation</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="inlineStr"/>
+      <c r="C36" s="4" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>validation.directory</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>9 - validation</t>
+        </is>
+      </c>
+      <c r="C37" s="7" t="inlineStr">
+        <is>
+          <t>Sub-folder name</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>validation.output_file</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>control_validation.csv</t>
+        </is>
+      </c>
+      <c r="C38" s="7" t="inlineStr">
+        <is>
+          <t>CSV output</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>validation.review_file</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>validation_review.xlsx</t>
+        </is>
+      </c>
+      <c r="C39" s="7" t="inlineStr">
+        <is>
+          <t>Human review workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t># Consolidated Report</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="inlineStr"/>
+      <c r="C40" s="4" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>consolidated_report.enabled</t>
+        </is>
+      </c>
+      <c r="B41" t="b">
+        <v>1</v>
+      </c>
+      <c r="C41" s="7" t="inlineStr">
+        <is>
+          <t>Build single .xlsx workbook after all steps</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
           <t>consolidated_report.filename_prefix</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="B42" t="inlineStr">
         <is>
           <t>DPS_Report</t>
         </is>
       </c>
-      <c r="C35" s="7" t="inlineStr">
+      <c r="C42" s="7" t="inlineStr">
         <is>
           <t>Prefix for timestamped filename</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C35"/>
+  <autoFilter ref="A1:C42"/>
   <dataValidations count="1">
-    <dataValidation sqref="B34" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid value" error="Please select TRUE or FALSE" type="list">
+    <dataValidation sqref="B41" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid value" error="Please select TRUE or FALSE" type="list">
       <formula1>"TRUE,FALSE"</formula1>
     </dataValidation>
   </dataValidations>
@@ -4815,11 +5771,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="65" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
     <col width="65" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
@@ -4897,13 +5853,94 @@
       <c r="B6" t="inlineStr"/>
       <c r="C6" s="5" t="inlineStr"/>
     </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t># Sections to Delete</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr"/>
+      <c r="C7" s="3" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>## Delete an entire section: heading + all content until the next heading of same or higher level.</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" s="5" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>## Match is case-insensitive substring on the heading text. Originals are never modified.</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" s="5" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>## Example: 'Appendix A' deletes the Appendix A heading and everything below it until the next H1/H2.</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" s="5" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Section Heading</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>Delete (TRUE/FALSE)</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr"/>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" s="5" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr"/>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" s="5" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr"/>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" s="5" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr"/>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" s="5" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr"/>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" s="5" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:C6"/>
-  <dataValidations count="2">
+  <autoFilter ref="A1:C16"/>
+  <dataValidations count="3">
     <dataValidation sqref="B3" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid value" error="Please select TRUE or FALSE" type="list">
       <formula1>"TRUE,FALSE"</formula1>
     </dataValidation>
     <dataValidation sqref="B4" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid value" error="Please select TRUE or FALSE" type="list">
+      <formula1>"TRUE,FALSE"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B12:B16" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid value" error="Please select TRUE or FALSE" type="list">
       <formula1>"TRUE,FALSE"</formula1>
     </dataValidation>
   </dataValidations>

--- a/dps_config.xlsx
+++ b/dps_config.xlsx
@@ -42,10 +42,10 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'Search Terms'!$A$1:$C$15</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'Control Extraction'!$A$1:$C$57</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'Pipeline'!$A$1:$E$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="15" hidden="1">'Metadata'!$A$1:$E$32</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="15" hidden="1">'Metadata'!$A$1:$E$36</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="16" hidden="1">'Docx2md'!$A$1:$C$36</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'Docx2jsonl'!$A$1:$C$14</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="18" hidden="1">'Acronym Finder'!$A$1:$C$24</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="18" hidden="1">'Acronym Finder'!$A$1:$C$99</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -54,7 +54,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -67,6 +67,27 @@
       <b val="1"/>
       <color rgb="002F5496"/>
       <sz val="14"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="002F5496"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <i val="1"/>
+      <color rgb="00666666"/>
+      <sz val="9"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -95,14 +116,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="002F5496"/>
-        <bgColor rgb="002F5496"/>
+        <fgColor rgb="00D6E4F0"/>
+        <bgColor rgb="00D6E4F0"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D6E4F0"/>
-        <bgColor rgb="00D6E4F0"/>
+        <fgColor rgb="002F5496"/>
+        <bgColor rgb="002F5496"/>
       </patternFill>
     </fill>
   </fills>
@@ -132,27 +153,33 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -518,10 +545,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A29"/>
+  <dimension ref="A1:C64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="80" customWidth="1" min="1" max="1"/>
+    <col width="38" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -530,183 +559,849 @@
           <t>DPS Configuration Workbook</t>
         </is>
       </c>
+      <c r="B1" t="inlineStr"/>
+      <c r="C1" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>This workbook controls every setting for the DPS pipeline.</t>
-        </is>
-      </c>
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Overview</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr"/>
+      <c r="C3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr"/>
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>This workbook is the central configuration file for the Document Processing System (DPS) pipeline.</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr"/>
+      <c r="C4" s="3" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>HOW TO USE:</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  1. Each sheet controls one section of the configuration.</t>
-        </is>
-      </c>
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Each worksheet controls a specific area of pipeline behavior. Edit the Value column on any sheet to customise settings; leave a cell blank to use the built-in default.</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr"/>
+      <c r="C5" s="3" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  2. Settings sheets have: Setting | Value | Description columns.</t>
-        </is>
-      </c>
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Quick-Start Checklist — Review Before First Run</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr"/>
+      <c r="C7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  3. List sheets have: Value | Description columns.</t>
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>Where to Find It</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>Default</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  4. Sub-headers (rows starting with #) separate groups — do NOT delete them.</t>
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>Input directory</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>Input sheet  &gt;  'directory' row</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>./input</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  5. Boolean fields have TRUE/FALSE dropdowns.</t>
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>Output directory</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Output sheet  &gt;  'directory' row</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>./output</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  6. Empty Value cells use the built-in default.</t>
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Steps to run</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>Pipeline sheet  &gt;  'Enabled' column</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>All enabled</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  7. Add new list items by inserting rows in the appropriate section.</t>
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>File pattern</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>Input sheet  &gt;  'pattern' row</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>*.docx</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr"/>
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Max chunk size</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Thresholds sheet  &gt;  'max_characters'</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>36 000 chars (~20 pages)</t>
+        </is>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>PIPELINE ORDER:</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Step 0  policy_profiler.py         — Scan &amp; classify all docs</t>
-        </is>
-      </c>
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>All other settings ship with sensible defaults. Adjust only when your environment requires it.</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Step 1  acronym_finder.py          — Scan for acronym candidates, generates an acronym audit workbook for human review and finalization. The confirmed set of acronyms are then fed into the metadata tagging stage</t>
-        </is>
-      </c>
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>How to Use This Workbook</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr"/>
+      <c r="C16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Step 2  extract_controls.py        — Pull structured controls from docx into an excel using regex and heuristics</t>
-        </is>
-      </c>
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>Guideline</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>Details</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Step 3  cross_reference_extractor.py — Capture cross-refs. This includes 'refer to section', URLs in documents, and internal document links to headings</t>
-        </is>
-      </c>
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>Column layout</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>Settings sheets use Setting | Value | Description columns. List sheets use Value | Description.</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Step 4  heading_style_fixer.py     — Fix false headings (Text that is bold and appears to be heading but is not a heading format for .docx)</t>
-        </is>
-      </c>
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>Sub-headers</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Rows starting with '#' are section dividers. Do not delete or modify them.</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Step 5  section_splitter.py        — Split docs at H1 boundaries after the desired char limit</t>
-        </is>
-      </c>
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>Boolean fields</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>Use the TRUE / FALSE dropdown. Manual text entry is not accepted.</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Step 6  add_metadata.py            — Stamp sub-docs with metadata</t>
-        </is>
-      </c>
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>Blank values</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>Leaving a Value cell empty tells the pipeline to use its built-in default.</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Step 7  docx2md.py                 — Convert word documents to Markdown</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Step 8  docx2jsonl.py              — Convert word documents to JSONL</t>
-        </is>
-      </c>
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>Adding list items</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Insert a new row in the appropriate section and fill in the Value column.</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Step 9  validate_controls.py       — Validate controls in split versions of docs</t>
-        </is>
-      </c>
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>Pipeline Execution Order</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr"/>
+      <c r="C24" s="2" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr"/>
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>Step</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>Script</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>HOW TO RUN:</t>
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>0 - Document Profiler</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>policy_profiler.py</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>Scans all documents, extracts metadata, classifies document types, scores priority, and counts words.</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Full pipeline:  python run_pipeline.py</t>
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>1 - Acronym Finder</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>acronym_finder.py</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>Identifies acronym candidates and generates an audit workbook for human review. Confirmed acronyms feed into the metadata tagging stage.</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Single step:    python run_pipeline.py --step 0</t>
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>2 - Control Extractor</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>extract_controls.py</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>Extracts structured control data from compliance documents into Excel using regex and heuristics.</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Range:          python run_pipeline.py --step 1-3</t>
-        </is>
-      </c>
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>3 - Cross-Reference Extractor</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>cross_reference_extractor.py</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>Captures cross-references including section references, URLs, and internal document heading links.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>4 - Heading Style Fixer</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>heading_style_fixer.py</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>Converts visually bold text that appears to be a heading into proper Word heading styles.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>5 - Section Splitter</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>section_splitter.py</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>Splits documents at Heading 1 boundaries once the character limit is exceeded.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>6 - Metadata Injector</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>add_metadata.py</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>Stamps each sub-document with identity and classification metadata.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>7 - DOCX to Markdown</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>docx2md.py</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>Converts Word documents to clean Markdown with YAML front matter.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>8 - DOCX to JSONL</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>docx2jsonl.py</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>Converts Word documents to chunked JSONL for RAG / vector-database ingestion.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>9 - Control Validator</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>validate_controls.py</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>Validates that all controls extracted in Step 2 are present in the Step 5 split documents.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>Sheet Reference</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr"/>
+      <c r="C37" s="2" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>Each worksheet below controls settings consumed by one or more pipeline scripts. The Reference Script column indicates which script reads the sheet at runtime.</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr"/>
+      <c r="C38" s="3" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>Sheet Name</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>Reference Script</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t>Purpose</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>Input</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>run_pipeline.py</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>Input folder, file pattern, and exclude patterns.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>Output</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>run_pipeline.py</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>Output folder structure and filenames for each step.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>Pipeline</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>run_pipeline.py</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>Enable or disable individual pipeline steps.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>Thresholds</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>section_splitter.py</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>Chunk-size limits and page-estimation parameters.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>Sections</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>policy_profiler.py</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>Keywords used to classify Purpose, Scope, and Controls sections.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>Headings</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>heading_style_fixer.py</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>Heading styles, custom style maps, and fake-heading detection rules.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>Text Deletions</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>heading_style_fixer.py</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>Phrases or entire sections to strip during processing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>Cross References</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>cross_reference_extractor.py</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>Cross-reference detection patterns.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>Tables</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>policy_profiler.py</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>Table-classification keywords.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>policy_profiler.py</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>Type A / B / C / D classification thresholds.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>Profiling Flags</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>policy_profiler.py</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>Flags for control-dense and heading-variance documents.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>Priority Scoring</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>policy_profiler.py</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="inlineStr">
+        <is>
+          <t>Weights for the priority-ranking algorithm.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>Search Terms</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>policy_profiler.py</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="inlineStr">
+        <is>
+          <t>Custom terms to surface in profiler output.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>Control Extraction</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>extract_controls.py</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="inlineStr">
+        <is>
+          <t>Control-ID patterns, whitelist, and blacklist.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>Metadata</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>add_metadata.py</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="inlineStr">
+        <is>
+          <t>Metadata fields, URL lookup table, and tag-generation rules.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="inlineStr">
+        <is>
+          <t>Docx2md</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t>docx2md.py</t>
+        </is>
+      </c>
+      <c r="C55" s="3" t="inlineStr">
+        <is>
+          <t>Markdown conversion settings and front-matter field mapping.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="inlineStr">
+        <is>
+          <t>Docx2jsonl</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>docx2jsonl.py</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="inlineStr">
+        <is>
+          <t>JSONL chunking parameters.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="inlineStr">
+        <is>
+          <t>Acronym Finder</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="inlineStr">
+        <is>
+          <t>acronym_finder.py</t>
+        </is>
+      </c>
+      <c r="C57" s="3" t="inlineStr">
+        <is>
+          <t>Acronym detection patterns and ignore list.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="5" t="inlineStr">
+        <is>
+          <t>Most sheets work correctly with defaults. Edit only for custom heading styles, special control-ID formats, or organisation-specific requirements.</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr"/>
+      <c r="C58" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>Running the Pipeline</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr"/>
+      <c r="C60" s="2" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="4" t="inlineStr">
+        <is>
+          <t>Command</t>
+        </is>
+      </c>
+      <c r="B61" s="4" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="3" t="inlineStr">
+        <is>
+          <t>python run_pipeline.py</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="inlineStr">
+        <is>
+          <t>Execute the full pipeline (all enabled steps).</t>
+        </is>
+      </c>
+      <c r="C62" s="3" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="3" t="inlineStr">
+        <is>
+          <t>python run_pipeline.py --step 0</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="inlineStr">
+        <is>
+          <t>Run a single step by its number.</t>
+        </is>
+      </c>
+      <c r="C63" s="3" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="3" t="inlineStr">
+        <is>
+          <t>python run_pipeline.py --step 1-3</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="inlineStr">
+        <is>
+          <t>Run a contiguous range of steps.</t>
+        </is>
+      </c>
+      <c r="C64" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -728,30 +1423,30 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>Setting</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="6" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="6" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="8" t="inlineStr">
         <is>
           <t># ControlDense</t>
         </is>
       </c>
-      <c r="B2" s="4" t="inlineStr"/>
-      <c r="C2" s="3" t="inlineStr"/>
+      <c r="B2" s="8" t="inlineStr"/>
+      <c r="C2" s="7" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -762,20 +1457,20 @@
       <c r="B3" t="n">
         <v>5</v>
       </c>
-      <c r="C3" s="6" t="inlineStr">
-        <is>
-          <t>Flag if &gt;= this many control IDs per approx page</t>
+      <c r="C3" s="10" t="inlineStr">
+        <is>
+          <t>Flag if &gt;= this many control IDs per approx page [default: 5.0]</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="8" t="inlineStr">
         <is>
           <t># HeadingVariance</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr"/>
-      <c r="C4" s="3" t="inlineStr"/>
+      <c r="B4" s="8" t="inlineStr"/>
+      <c r="C4" s="7" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -786,9 +1481,9 @@
       <c r="B5" t="n">
         <v>2</v>
       </c>
-      <c r="C5" s="6" t="inlineStr">
-        <is>
-          <t>Flag if &gt;= this many heading level jumps (e.g., H1→H3)</t>
+      <c r="C5" s="10" t="inlineStr">
+        <is>
+          <t>Flag if &gt;= this many heading level jumps (e.g., H1→H3) [default: 2]</t>
         </is>
       </c>
     </row>
@@ -801,20 +1496,20 @@
       <c r="B6" t="n">
         <v>0.5</v>
       </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>Flag if &gt;= X% of headings are fake (0.5 = 50%)</t>
+      <c r="C6" s="10" t="inlineStr">
+        <is>
+          <t>Flag if &gt;= X% of headings are fake (0.5 = 50%) [default: 0.5]</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t># TableDense</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr"/>
-      <c r="C7" s="3" t="inlineStr"/>
+      <c r="B7" s="8" t="inlineStr"/>
+      <c r="C7" s="7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -825,9 +1520,9 @@
       <c r="B8" t="n">
         <v>30</v>
       </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>Flag if &gt;= X% table content (early warning)</t>
+      <c r="C8" s="10" t="inlineStr">
+        <is>
+          <t>Flag if &gt;= X% table content (early warning) [default: 30]</t>
         </is>
       </c>
     </row>
@@ -852,30 +1547,30 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>Setting</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="6" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="6" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="8" t="inlineStr">
         <is>
           <t># RAG Chunk Size</t>
         </is>
       </c>
-      <c r="B2" s="4" t="inlineStr"/>
-      <c r="C2" s="3" t="inlineStr"/>
+      <c r="B2" s="8" t="inlineStr"/>
+      <c r="C2" s="7" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -886,9 +1581,9 @@
       <c r="B3" t="n">
         <v>36000</v>
       </c>
-      <c r="C3" s="6" t="inlineStr">
-        <is>
-          <t>Max chars per split sub-document. 36000≈20pp, 18000≈10pp, 72000≈40pp</t>
+      <c r="C3" s="10" t="inlineStr">
+        <is>
+          <t>Max chars per split sub-document. 36000≈20pp, 18000≈10pp, 72000≈40pp [default: 36000]</t>
         </is>
       </c>
     </row>
@@ -901,20 +1596,20 @@
       <c r="B4" t="n">
         <v>20</v>
       </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>Approximate page equivalent (reporting only)</t>
+      <c r="C4" s="10" t="inlineStr">
+        <is>
+          <t>Approximate page equivalent (reporting only) [default: 20]</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="8" t="inlineStr">
         <is>
           <t># Estimation Ratios</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr"/>
-      <c r="C5" s="3" t="inlineStr"/>
+      <c r="B5" s="8" t="inlineStr"/>
+      <c r="C5" s="7" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -925,9 +1620,9 @@
       <c r="B6" t="n">
         <v>30</v>
       </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>approx_pages = total_paragraphs / this. Lower=more pages</t>
+      <c r="C6" s="10" t="inlineStr">
+        <is>
+          <t>approx_pages = total_paragraphs / this. Lower=more pages [default: 30]</t>
         </is>
       </c>
     </row>
@@ -940,20 +1635,20 @@
       <c r="B7" t="n">
         <v>1800</v>
       </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>Chars per page for split manifest estimates</t>
+      <c r="C7" s="10" t="inlineStr">
+        <is>
+          <t>Chars per page for split manifest estimates [default: 1800]</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="8" t="inlineStr">
         <is>
           <t># Flagging Thresholds</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr"/>
-      <c r="C8" s="3" t="inlineStr"/>
+      <c r="B8" s="8" t="inlineStr"/>
+      <c r="C8" s="7" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -964,9 +1659,9 @@
       <c r="B9" t="n">
         <v>50</v>
       </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>Flag sections exceeding this % of total doc length</t>
+      <c r="C9" s="10" t="inlineStr">
+        <is>
+          <t>Flag sections exceeding this % of total doc length [default: 50]</t>
         </is>
       </c>
     </row>
@@ -979,9 +1674,9 @@
       <c r="B10" t="n">
         <v>10</v>
       </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>Flag docs with more tables than this</t>
+      <c r="C10" s="10" t="inlineStr">
+        <is>
+          <t>Flag docs with more tables than this [default: 10]</t>
         </is>
       </c>
     </row>
@@ -1002,46 +1697,46 @@
   <cols>
     <col width="65" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="52" customWidth="1" min="3" max="3"/>
+    <col width="65" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>Setting</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="6" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="6" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t># Scoring Weights</t>
         </is>
       </c>
-      <c r="B2" s="4" t="inlineStr"/>
-      <c r="C2" s="4" t="inlineStr"/>
+      <c r="B2" s="8" t="inlineStr"/>
+      <c r="C2" s="7" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="inlineStr">
+      <c r="A3" s="10" t="inlineStr">
         <is>
           <t>## Higher weight = more impact on priority score. Adjust ratios to change emphasis.</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
+      <c r="C3" s="9" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" s="9" t="inlineStr">
         <is>
           <t>table_count</t>
         </is>
@@ -1049,14 +1744,14 @@
       <c r="B4" t="n">
         <v>2</v>
       </c>
-      <c r="C4" s="7" t="inlineStr">
-        <is>
-          <t>More tables = harder to optimize</t>
+      <c r="C4" s="10" t="inlineStr">
+        <is>
+          <t>More tables = harder to optimize [default: 2.0]</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" s="9" t="inlineStr">
         <is>
           <t>cross_ref_count</t>
         </is>
@@ -1064,14 +1759,14 @@
       <c r="B5" t="n">
         <v>1.5</v>
       </c>
-      <c r="C5" s="7" t="inlineStr">
-        <is>
-          <t>More cross-refs = more manual work</t>
+      <c r="C5" s="10" t="inlineStr">
+        <is>
+          <t>More cross-refs = more manual work [default: 1.5]</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="A6" s="9" t="inlineStr">
         <is>
           <t>fake_heading_count</t>
         </is>
@@ -1079,14 +1774,14 @@
       <c r="B6" t="n">
         <v>1</v>
       </c>
-      <c r="C6" s="7" t="inlineStr">
-        <is>
-          <t>Fake headings break chunking</t>
+      <c r="C6" s="10" t="inlineStr">
+        <is>
+          <t>Fake headings break chunking [default: 1.0]</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" s="9" t="inlineStr">
         <is>
           <t>page_count</t>
         </is>
@@ -1094,14 +1789,14 @@
       <c r="B7" t="n">
         <v>0.5</v>
       </c>
-      <c r="C7" s="7" t="inlineStr">
-        <is>
-          <t>Longer docs need more splitting</t>
+      <c r="C7" s="10" t="inlineStr">
+        <is>
+          <t>Longer docs need more splitting [default: 0.5]</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="A8" s="9" t="inlineStr">
         <is>
           <t>missing_sections</t>
         </is>
@@ -1109,14 +1804,14 @@
       <c r="B8" t="n">
         <v>1.5</v>
       </c>
-      <c r="C8" s="7" t="inlineStr">
-        <is>
-          <t>Missing standard sections = structural problems</t>
+      <c r="C8" s="10" t="inlineStr">
+        <is>
+          <t>Missing standard sections = structural problems [default: 1.5]</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="A9" s="9" t="inlineStr">
         <is>
           <t>merged_cells</t>
         </is>
@@ -1124,14 +1819,14 @@
       <c r="B9" t="n">
         <v>1</v>
       </c>
-      <c r="C9" s="7" t="inlineStr">
-        <is>
-          <t>Merged cells complicate table flattening</t>
+      <c r="C9" s="10" t="inlineStr">
+        <is>
+          <t>Merged cells complicate table flattening [default: 1.0]</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="A10" s="9" t="inlineStr">
         <is>
           <t>over_size_limit</t>
         </is>
@@ -1139,57 +1834,57 @@
       <c r="B10" t="n">
         <v>3</v>
       </c>
-      <c r="C10" s="7" t="inlineStr">
-        <is>
-          <t>Over character limit is a hard retrieval problem</t>
+      <c r="C10" s="10" t="inlineStr">
+        <is>
+          <t>Over character limit is a hard retrieval problem [default: 3.0]</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" s="7" t="inlineStr">
         <is>
           <t># Usage Frequency</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr"/>
-      <c r="C11" s="4" t="inlineStr"/>
+      <c r="B11" s="8" t="inlineStr"/>
+      <c r="C11" s="7" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="6" t="inlineStr">
+      <c r="A12" s="10" t="inlineStr">
         <is>
           <t>## Per-document usage (0-10). Multiplied by 2.0 and added to priority.</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
+      <c r="C12" s="9" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="8" t="inlineStr">
+      <c r="A13" s="12" t="inlineStr">
         <is>
           <t>## Filename (exact match)</t>
         </is>
       </c>
-      <c r="B13" s="9" t="inlineStr">
+      <c r="B13" s="13" t="inlineStr">
         <is>
           <t>Frequency (0-10)</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr"/>
+      <c r="C13" s="9" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="inlineStr"/>
+      <c r="A14" s="9" t="inlineStr"/>
       <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr"/>
+      <c r="C14" s="9" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr"/>
+      <c r="A15" s="9" t="inlineStr"/>
       <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr"/>
+      <c r="C15" s="9" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="inlineStr"/>
+      <c r="A16" s="9" t="inlineStr"/>
       <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr"/>
+      <c r="C16" s="9" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:C16"/>
@@ -1212,33 +1907,33 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>Setting</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="6" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="6" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t># Settings</t>
         </is>
       </c>
-      <c r="B2" s="4" t="inlineStr"/>
-      <c r="C2" s="3" t="inlineStr"/>
+      <c r="B2" s="8" t="inlineStr"/>
+      <c r="C2" s="7" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" s="9" t="inlineStr">
         <is>
           <t>enabled</t>
         </is>
@@ -1246,14 +1941,14 @@
       <c r="B3" t="b">
         <v>1</v>
       </c>
-      <c r="C3" s="6" t="inlineStr">
-        <is>
-          <t>Enable key term search in profiler</t>
+      <c r="C3" s="10" t="inlineStr">
+        <is>
+          <t>Enable key term search in profiler [default: TRUE]</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" s="9" t="inlineStr">
         <is>
           <t>match_mode</t>
         </is>
@@ -1263,14 +1958,14 @@
           <t>word</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>"word" = whole-word boundary, "substring" = anywhere in text</t>
+      <c r="C4" s="10" t="inlineStr">
+        <is>
+          <t>"word" = whole-word boundary, "substring" = anywhere in text [default: word]</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" s="9" t="inlineStr">
         <is>
           <t>show_counts</t>
         </is>
@@ -1278,81 +1973,81 @@
       <c r="B5" t="b">
         <v>1</v>
       </c>
-      <c r="C5" s="6" t="inlineStr">
-        <is>
-          <t>TRUE = show occurrence count, FALSE = show YES/blank</t>
+      <c r="C5" s="10" t="inlineStr">
+        <is>
+          <t>TRUE = show occurrence count, FALSE = show YES/blank [default: TRUE]</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t># Terms</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr"/>
-      <c r="C6" s="3" t="inlineStr"/>
+      <c r="B6" s="8" t="inlineStr"/>
+      <c r="C6" s="7" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="inlineStr">
+      <c r="A7" s="10" t="inlineStr">
         <is>
           <t>## Each term gets its own column in the Excel output. One per row.</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
-      <c r="C7" s="5" t="inlineStr"/>
+      <c r="C7" s="9" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="A8" s="9" t="inlineStr">
         <is>
           <t>AC</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
-      <c r="C8" s="5" t="inlineStr"/>
+      <c r="C8" s="9" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="A9" s="9" t="inlineStr">
         <is>
           <t>Cloud</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
-      <c r="C9" s="5" t="inlineStr"/>
+      <c r="C9" s="9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="A10" s="9" t="inlineStr">
         <is>
           <t>NIST</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
-      <c r="C10" s="5" t="inlineStr"/>
+      <c r="C10" s="9" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="inlineStr"/>
+      <c r="A11" s="9" t="inlineStr"/>
       <c r="B11" t="inlineStr"/>
-      <c r="C11" s="5" t="inlineStr"/>
+      <c r="C11" s="9" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="inlineStr"/>
+      <c r="A12" s="9" t="inlineStr"/>
       <c r="B12" t="inlineStr"/>
-      <c r="C12" s="5" t="inlineStr"/>
+      <c r="C12" s="9" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="inlineStr"/>
+      <c r="A13" s="9" t="inlineStr"/>
       <c r="B13" t="inlineStr"/>
-      <c r="C13" s="5" t="inlineStr"/>
+      <c r="C13" s="9" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="inlineStr"/>
+      <c r="A14" s="9" t="inlineStr"/>
       <c r="B14" t="inlineStr"/>
-      <c r="C14" s="5" t="inlineStr"/>
+      <c r="C14" s="9" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr"/>
+      <c r="A15" s="9" t="inlineStr"/>
       <c r="B15" t="inlineStr"/>
-      <c r="C15" s="5" t="inlineStr"/>
+      <c r="C15" s="9" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:C15"/>
@@ -1386,675 +2081,675 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>Setting</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="6" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="6" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t># Common Settings</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr"/>
-      <c r="C2" s="3" t="inlineStr"/>
+      <c r="B2" s="7" t="inlineStr"/>
+      <c r="C2" s="7" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" s="9" t="inlineStr">
         <is>
           <t>require_bold_control_id</t>
         </is>
       </c>
-      <c r="B3" s="5" t="b">
+      <c r="B3" s="9" t="b">
         <v>1</v>
       </c>
-      <c r="C3" s="6" t="inlineStr">
-        <is>
-          <t>Only extract control IDs that appear in bold text. Set FALSE if your IDs are not bold</t>
+      <c r="C3" s="10" t="inlineStr">
+        <is>
+          <t>Only extract control IDs that appear in bold text. Set FALSE if your IDs are not bold [default: TRUE]</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" s="9" t="inlineStr">
         <is>
           <t>bold_fallback_if_zero</t>
         </is>
       </c>
-      <c r="B4" s="5" t="b">
+      <c r="B4" s="9" t="b">
         <v>1</v>
       </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>If bold-only extraction finds 0 controls in a doc, auto-retry without the bold requirement</t>
+      <c r="C4" s="10" t="inlineStr">
+        <is>
+          <t>If bold-only extraction finds 0 controls in a doc, auto-retry without the bold requirement [default: TRUE]</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" s="9" t="inlineStr">
         <is>
           <t>tables_ignore_bold</t>
         </is>
       </c>
-      <c r="B5" s="5" t="b">
+      <c r="B5" s="9" t="b">
         <v>1</v>
       </c>
-      <c r="C5" s="6" t="inlineStr">
-        <is>
-          <t>Always extract control IDs from table cells regardless of bold setting</t>
+      <c r="C5" s="10" t="inlineStr">
+        <is>
+          <t>Always extract control IDs from table cells regardless of bold setting [default: TRUE]</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="A6" s="9" t="inlineStr">
         <is>
           <t>control_id_anchor_start</t>
         </is>
       </c>
-      <c r="B6" s="5" t="b">
+      <c r="B6" s="9" t="b">
         <v>0</v>
       </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>Only match control IDs near the start of a paragraph (filters out inline references)</t>
+      <c r="C6" s="10" t="inlineStr">
+        <is>
+          <t>Only match control IDs near the start of a paragraph (filters out inline references) [default: FALSE]</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" s="9" t="inlineStr">
         <is>
           <t>control_id_start_chars</t>
         </is>
       </c>
-      <c r="B7" s="5" t="n">
+      <c r="B7" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>How many chars from paragraph start to search when anchor_start is enabled</t>
+      <c r="C7" s="10" t="inlineStr">
+        <is>
+          <t>How many chars from paragraph start to search when anchor_start is enabled [default: 25]</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="A8" s="9" t="inlineStr">
         <is>
           <t>min_control_block_lines</t>
         </is>
       </c>
-      <c r="B8" s="5" t="n">
+      <c r="B8" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>Discard control blocks with fewer than N content lines. 0 = keep all. 2 = drop inline refs</t>
+      <c r="C8" s="10" t="inlineStr">
+        <is>
+          <t>Discard control blocks with fewer than N content lines. 0 = keep all. 2 = drop inline refs [default: 0]</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="A9" s="9" t="inlineStr">
         <is>
           <t>enable_checkpoint</t>
         </is>
       </c>
-      <c r="B9" s="5" t="b">
+      <c r="B9" s="9" t="b">
         <v>1</v>
       </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>Save progress so re-runs skip already-processed files. Delete checkpoint.json to force fresh run</t>
+      <c r="C9" s="10" t="inlineStr">
+        <is>
+          <t>Save progress so re-runs skip already-processed files. Delete checkpoint.json to force fresh run [default: TRUE]</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="A10" s="9" t="inlineStr">
         <is>
           <t>output_format</t>
         </is>
       </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="B10" s="9" t="inlineStr">
         <is>
           <t>both</t>
         </is>
       </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>"csv", "xlsx", or "both" — controls the output file format for extracted controls</t>
+      <c r="C10" s="10" t="inlineStr">
+        <is>
+          <t>"csv", "xlsx", or "both" — controls the output file format for extracted controls [default: both]</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" s="7" t="inlineStr">
         <is>
           <t># Control ID Patterns (Regex)</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr"/>
-      <c r="C11" s="3" t="inlineStr"/>
+      <c r="B11" s="7" t="inlineStr"/>
+      <c r="C11" s="7" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="6" t="inlineStr">
+      <c r="A12" s="10" t="inlineStr">
         <is>
           <t>## Regex patterns to match control IDs in document text. One pattern per row.</t>
         </is>
       </c>
-      <c r="B12" s="5" t="inlineStr"/>
-      <c r="C12" s="5" t="inlineStr"/>
+      <c r="B12" s="9" t="inlineStr"/>
+      <c r="C12" s="9" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="6" t="inlineStr">
+      <c r="A13" s="10" t="inlineStr">
         <is>
           <t>## Examples matched: AC-1.001, IR001.002, CFG.1.0042, AUP 1.001</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr"/>
-      <c r="C13" s="5" t="inlineStr"/>
+      <c r="B13" s="9" t="inlineStr"/>
+      <c r="C13" s="9" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="6" t="inlineStr">
+      <c r="A14" s="10" t="inlineStr">
         <is>
           <t>## If zero controls extracted, your IDs use a different format — add a pattern here.</t>
         </is>
       </c>
-      <c r="B14" s="5" t="inlineStr"/>
-      <c r="C14" s="5" t="inlineStr"/>
+      <c r="B14" s="9" t="inlineStr"/>
+      <c r="C14" s="9" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="6" t="inlineStr">
+      <c r="A15" s="10" t="inlineStr">
         <is>
           <t>## Test patterns at regex101.com before adding.</t>
         </is>
       </c>
-      <c r="B15" s="5" t="inlineStr"/>
-      <c r="C15" s="5" t="inlineStr"/>
+      <c r="B15" s="9" t="inlineStr"/>
+      <c r="C15" s="9" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="inlineStr">
+      <c r="A16" s="9" t="inlineStr">
         <is>
           <t>\b[A-Z]{2,4}[-.]?\d{1,3}[-.]\d{2,4}\b</t>
         </is>
       </c>
-      <c r="B16" s="5" t="inlineStr"/>
-      <c r="C16" s="5" t="inlineStr"/>
+      <c r="B16" s="9" t="inlineStr"/>
+      <c r="C16" s="9" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="inlineStr">
+      <c r="A17" s="9" t="inlineStr">
         <is>
           <t>\b[A-Z]{2,4}\s+\d{1,3}\.\d{2,4}\b</t>
         </is>
       </c>
-      <c r="B17" s="5" t="inlineStr"/>
-      <c r="C17" s="5" t="inlineStr"/>
+      <c r="B17" s="9" t="inlineStr"/>
+      <c r="C17" s="9" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="inlineStr">
+      <c r="A18" s="9" t="inlineStr">
         <is>
           <t>\b[A-Z]{2,4}\d{2,3}\.\d{2,4}\b</t>
         </is>
       </c>
-      <c r="B18" s="5" t="inlineStr"/>
-      <c r="C18" s="5" t="inlineStr"/>
+      <c r="B18" s="9" t="inlineStr"/>
+      <c r="C18" s="9" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="inlineStr">
+      <c r="A19" s="7" t="inlineStr">
         <is>
           <t># Whitelist / Blacklist</t>
         </is>
       </c>
-      <c r="B19" s="3" t="inlineStr"/>
-      <c r="C19" s="3" t="inlineStr"/>
+      <c r="B19" s="7" t="inlineStr"/>
+      <c r="C19" s="7" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="6" t="inlineStr">
+      <c r="A20" s="10" t="inlineStr">
         <is>
           <t>## One control ID per row. Type = "whitelist" or "blacklist".</t>
         </is>
       </c>
-      <c r="B20" s="5" t="inlineStr"/>
-      <c r="C20" s="5" t="inlineStr"/>
+      <c r="B20" s="9" t="inlineStr"/>
+      <c r="C20" s="9" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="6" t="inlineStr">
+      <c r="A21" s="10" t="inlineStr">
         <is>
           <t>## Whitelist: if ANY whitelist entries exist, ONLY matching controls are kept.</t>
         </is>
       </c>
-      <c r="B21" s="5" t="inlineStr"/>
-      <c r="C21" s="5" t="inlineStr"/>
+      <c r="B21" s="9" t="inlineStr"/>
+      <c r="C21" s="9" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="6" t="inlineStr">
+      <c r="A22" s="10" t="inlineStr">
         <is>
           <t>## Blacklist: matching controls are excluded (applied after whitelist).</t>
         </is>
       </c>
-      <c r="B22" s="5" t="inlineStr"/>
-      <c r="C22" s="5" t="inlineStr"/>
+      <c r="B22" s="9" t="inlineStr"/>
+      <c r="C22" s="9" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="6" t="inlineStr">
+      <c r="A23" s="10" t="inlineStr">
         <is>
           <t>## Supports exact IDs (e.g. AC-1.001) and prefix wildcards (e.g. AC-*).</t>
         </is>
       </c>
-      <c r="B23" s="5" t="inlineStr"/>
-      <c r="C23" s="5" t="inlineStr"/>
+      <c r="B23" s="9" t="inlineStr"/>
+      <c r="C23" s="9" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="6" t="inlineStr">
+      <c r="A24" s="10" t="inlineStr">
         <is>
           <t>## Add as many rows as needed. Leave this section empty to keep all controls.</t>
         </is>
       </c>
-      <c r="B24" s="5" t="inlineStr"/>
-      <c r="C24" s="5" t="inlineStr"/>
+      <c r="B24" s="9" t="inlineStr"/>
+      <c r="C24" s="9" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="inlineStr">
+      <c r="A25" s="7" t="inlineStr">
         <is>
           <t># Guidance Keywords</t>
         </is>
       </c>
-      <c r="B25" s="3" t="inlineStr"/>
-      <c r="C25" s="3" t="inlineStr"/>
+      <c r="B25" s="7" t="inlineStr"/>
+      <c r="C25" s="7" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="6" t="inlineStr">
+      <c r="A26" s="10" t="inlineStr">
         <is>
           <t>## Keywords marking the boundary between control description and supplemental guidance.</t>
         </is>
       </c>
-      <c r="B26" s="5" t="inlineStr"/>
-      <c r="C26" s="5" t="inlineStr"/>
+      <c r="B26" s="9" t="inlineStr"/>
+      <c r="C26" s="9" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="6" t="inlineStr">
-        <is>
-          <t>## One keyword per row. When a paragraph contains one of these, text after it is classified as guidance.</t>
-        </is>
-      </c>
-      <c r="B27" s="5" t="inlineStr"/>
-      <c r="C27" s="5" t="inlineStr"/>
+      <c r="A27" s="10" t="inlineStr">
+        <is>
+          <t>## Column A = keyword (one per row). When a paragraph contains one of these, text after it is classified as guidance.</t>
+        </is>
+      </c>
+      <c r="B27" s="9" t="inlineStr"/>
+      <c r="C27" s="9" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="5" t="inlineStr">
+      <c r="A28" s="9" t="inlineStr">
         <is>
           <t>implementation guidance</t>
         </is>
       </c>
-      <c r="B28" s="5" t="inlineStr"/>
-      <c r="C28" s="5" t="inlineStr"/>
+      <c r="B28" s="9" t="inlineStr"/>
+      <c r="C28" s="9" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="5" t="inlineStr">
+      <c r="A29" s="9" t="inlineStr">
         <is>
           <t>implementation:</t>
         </is>
       </c>
-      <c r="B29" s="5" t="inlineStr"/>
-      <c r="C29" s="5" t="inlineStr"/>
+      <c r="B29" s="9" t="inlineStr"/>
+      <c r="C29" s="9" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="5" t="inlineStr">
+      <c r="A30" s="9" t="inlineStr">
         <is>
           <t>guidelines:</t>
         </is>
       </c>
-      <c r="B30" s="5" t="inlineStr"/>
-      <c r="C30" s="5" t="inlineStr"/>
+      <c r="B30" s="9" t="inlineStr"/>
+      <c r="C30" s="9" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="5" t="inlineStr">
+      <c r="A31" s="9" t="inlineStr">
         <is>
           <t>how to implement</t>
         </is>
       </c>
-      <c r="B31" s="5" t="inlineStr"/>
-      <c r="C31" s="5" t="inlineStr"/>
+      <c r="B31" s="9" t="inlineStr"/>
+      <c r="C31" s="9" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="5" t="inlineStr">
+      <c r="A32" s="9" t="inlineStr">
         <is>
           <t>supplemental guidance</t>
         </is>
       </c>
-      <c r="B32" s="5" t="inlineStr"/>
-      <c r="C32" s="5" t="inlineStr"/>
+      <c r="B32" s="9" t="inlineStr"/>
+      <c r="C32" s="9" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="3" t="inlineStr">
+      <c r="A33" s="7" t="inlineStr">
         <is>
           <t># Metadata Triggers</t>
         </is>
       </c>
-      <c r="B33" s="3" t="inlineStr"/>
-      <c r="C33" s="3" t="inlineStr"/>
+      <c r="B33" s="7" t="inlineStr"/>
+      <c r="C33" s="7" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="6" t="inlineStr">
+      <c r="A34" s="10" t="inlineStr">
         <is>
           <t>## Category | Keyword — triggers for extracting document-level metadata (purpose, scope, applicability).</t>
         </is>
       </c>
-      <c r="B34" s="5" t="inlineStr"/>
-      <c r="C34" s="5" t="inlineStr"/>
+      <c r="B34" s="9" t="inlineStr"/>
+      <c r="C34" s="9" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="6" t="inlineStr">
+      <c r="A35" s="10" t="inlineStr">
         <is>
           <t>## Column A = category name, Column B = keyword. Multiple keywords per category are allowed (one per row).</t>
         </is>
       </c>
-      <c r="B35" s="5" t="inlineStr"/>
-      <c r="C35" s="5" t="inlineStr"/>
+      <c r="B35" s="9" t="inlineStr"/>
+      <c r="C35" s="9" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="6" t="inlineStr">
+      <c r="A36" s="10" t="inlineStr">
         <is>
           <t>## The extractor scans the first N paragraphs (see metadata_scan_paragraphs) for these keywords.</t>
         </is>
       </c>
-      <c r="B36" s="5" t="inlineStr"/>
-      <c r="C36" s="5" t="inlineStr"/>
+      <c r="B36" s="9" t="inlineStr"/>
+      <c r="C36" s="9" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="5" t="inlineStr">
+      <c r="A37" s="9" t="inlineStr">
         <is>
           <t>purpose</t>
         </is>
       </c>
-      <c r="B37" s="5" t="inlineStr">
+      <c r="B37" s="9" t="inlineStr">
         <is>
           <t>purpose</t>
         </is>
       </c>
-      <c r="C37" s="5" t="inlineStr"/>
+      <c r="C37" s="9" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="5" t="inlineStr">
+      <c r="A38" s="9" t="inlineStr">
         <is>
           <t>purpose</t>
         </is>
       </c>
-      <c r="B38" s="5" t="inlineStr">
+      <c r="B38" s="9" t="inlineStr">
         <is>
           <t>objective</t>
         </is>
       </c>
-      <c r="C38" s="5" t="inlineStr"/>
+      <c r="C38" s="9" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="5" t="inlineStr">
+      <c r="A39" s="9" t="inlineStr">
         <is>
           <t>purpose</t>
         </is>
       </c>
-      <c r="B39" s="5" t="inlineStr">
+      <c r="B39" s="9" t="inlineStr">
         <is>
           <t>intent</t>
         </is>
       </c>
-      <c r="C39" s="5" t="inlineStr"/>
+      <c r="C39" s="9" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="5" t="inlineStr">
+      <c r="A40" s="9" t="inlineStr">
         <is>
           <t>scope</t>
         </is>
       </c>
-      <c r="B40" s="5" t="inlineStr">
+      <c r="B40" s="9" t="inlineStr">
         <is>
           <t>scope</t>
         </is>
       </c>
-      <c r="C40" s="5" t="inlineStr"/>
+      <c r="C40" s="9" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="5" t="inlineStr">
+      <c r="A41" s="9" t="inlineStr">
         <is>
           <t>scope</t>
         </is>
       </c>
-      <c r="B41" s="5" t="inlineStr">
+      <c r="B41" s="9" t="inlineStr">
         <is>
           <t>coverage</t>
         </is>
       </c>
-      <c r="C41" s="5" t="inlineStr"/>
+      <c r="C41" s="9" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="5" t="inlineStr">
+      <c r="A42" s="9" t="inlineStr">
         <is>
           <t>scope</t>
         </is>
       </c>
-      <c r="B42" s="5" t="inlineStr">
+      <c r="B42" s="9" t="inlineStr">
         <is>
           <t>boundary</t>
         </is>
       </c>
-      <c r="C42" s="5" t="inlineStr"/>
+      <c r="C42" s="9" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="5" t="inlineStr">
+      <c r="A43" s="9" t="inlineStr">
         <is>
           <t>applicability</t>
         </is>
       </c>
-      <c r="B43" s="5" t="inlineStr">
+      <c r="B43" s="9" t="inlineStr">
         <is>
           <t>applicability</t>
         </is>
       </c>
-      <c r="C43" s="5" t="inlineStr"/>
+      <c r="C43" s="9" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="5" t="inlineStr">
+      <c r="A44" s="9" t="inlineStr">
         <is>
           <t>applicability</t>
         </is>
       </c>
-      <c r="B44" s="5" t="inlineStr">
+      <c r="B44" s="9" t="inlineStr">
         <is>
           <t>applies to</t>
         </is>
       </c>
-      <c r="C44" s="5" t="inlineStr"/>
+      <c r="C44" s="9" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="5" t="inlineStr">
+      <c r="A45" s="9" t="inlineStr">
         <is>
           <t>applicability</t>
         </is>
       </c>
-      <c r="B45" s="5" t="inlineStr">
+      <c r="B45" s="9" t="inlineStr">
         <is>
           <t>applies for</t>
         </is>
       </c>
-      <c r="C45" s="5" t="inlineStr"/>
+      <c r="C45" s="9" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="3" t="inlineStr">
+      <c r="A46" s="7" t="inlineStr">
         <is>
           <t># Heading Detection (Advanced)</t>
         </is>
       </c>
-      <c r="B46" s="3" t="inlineStr"/>
-      <c r="C46" s="3" t="inlineStr"/>
+      <c r="B46" s="7" t="inlineStr"/>
+      <c r="C46" s="7" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="5" t="inlineStr">
+      <c r="A47" s="9" t="inlineStr">
         <is>
           <t>heading_detection.use_word_heading_style</t>
         </is>
       </c>
-      <c r="B47" s="5" t="b">
+      <c r="B47" s="9" t="b">
         <v>1</v>
       </c>
-      <c r="C47" s="6" t="inlineStr">
-        <is>
-          <t>Use Word heading styles for detection</t>
+      <c r="C47" s="10" t="inlineStr">
+        <is>
+          <t>Use Word heading styles for detection [default: TRUE]</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="5" t="inlineStr">
+      <c r="A48" s="9" t="inlineStr">
         <is>
           <t>heading_detection.section_keyword_pattern</t>
         </is>
       </c>
-      <c r="B48" s="5" t="inlineStr">
+      <c r="B48" s="9" t="inlineStr">
         <is>
           <t>^[Ss]ection\s+\d{1,2}</t>
         </is>
       </c>
-      <c r="C48" s="6" t="inlineStr">
+      <c r="C48" s="10" t="inlineStr">
         <is>
           <t>Regex for section headings like "Section 4"</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="5" t="inlineStr">
+      <c r="A49" s="9" t="inlineStr">
         <is>
           <t>heading_detection.numbered_title_pattern</t>
         </is>
       </c>
-      <c r="B49" s="5" t="inlineStr">
+      <c r="B49" s="9" t="inlineStr">
         <is>
           <t>^\d{1,2}\.?\d{0,2}\s+[A-Z][a-zA-Z\s]{3,50}$</t>
         </is>
       </c>
-      <c r="C49" s="6" t="inlineStr">
+      <c r="C49" s="10" t="inlineStr">
         <is>
           <t>Regex for numbered titles like "4.1 Access Control"</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="5" t="inlineStr">
+      <c r="A50" s="9" t="inlineStr">
         <is>
           <t>heading_detection.detect_allcaps</t>
         </is>
       </c>
-      <c r="B50" s="5" t="b">
+      <c r="B50" s="9" t="b">
         <v>1</v>
       </c>
-      <c r="C50" s="6" t="inlineStr">
-        <is>
-          <t>Detect ALL CAPS headings</t>
+      <c r="C50" s="10" t="inlineStr">
+        <is>
+          <t>Detect ALL CAPS headings [default: TRUE]</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="5" t="inlineStr">
+      <c r="A51" s="9" t="inlineStr">
         <is>
           <t>heading_detection.allcaps_max_length</t>
         </is>
       </c>
-      <c r="B51" s="5" t="n">
+      <c r="B51" s="9" t="n">
         <v>80</v>
       </c>
-      <c r="C51" s="6" t="inlineStr">
-        <is>
-          <t>Max chars for all-caps heading</t>
+      <c r="C51" s="10" t="inlineStr">
+        <is>
+          <t>Max chars for all-caps heading [default: 80]</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="5" t="inlineStr">
+      <c r="A52" s="9" t="inlineStr">
         <is>
           <t>heading_detection.allcaps_min_words</t>
         </is>
       </c>
-      <c r="B52" s="5" t="n">
+      <c r="B52" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="C52" s="6" t="inlineStr">
-        <is>
-          <t>Min words for all-caps heading</t>
+      <c r="C52" s="10" t="inlineStr">
+        <is>
+          <t>Min words for all-caps heading [default: 3]</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="5" t="inlineStr">
+      <c r="A53" s="9" t="inlineStr">
         <is>
           <t>heading_detection.detect_bold_short</t>
         </is>
       </c>
-      <c r="B53" s="5" t="b">
+      <c r="B53" s="9" t="b">
         <v>1</v>
       </c>
-      <c r="C53" s="6" t="inlineStr">
-        <is>
-          <t>Detect short bold text as headings</t>
+      <c r="C53" s="10" t="inlineStr">
+        <is>
+          <t>Detect short bold text as headings [default: TRUE]</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="5" t="inlineStr">
+      <c r="A54" s="9" t="inlineStr">
         <is>
           <t>heading_detection.bold_max_length</t>
         </is>
       </c>
-      <c r="B54" s="5" t="n">
+      <c r="B54" s="9" t="n">
         <v>60</v>
       </c>
-      <c r="C54" s="6" t="inlineStr">
-        <is>
-          <t>Max chars for bold heading</t>
+      <c r="C54" s="10" t="inlineStr">
+        <is>
+          <t>Max chars for bold heading [default: 60]</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="3" t="inlineStr">
+      <c r="A55" s="7" t="inlineStr">
         <is>
           <t># Implementation Trigger (Regex)</t>
         </is>
       </c>
-      <c r="B55" s="3" t="inlineStr"/>
-      <c r="C55" s="3" t="inlineStr"/>
+      <c r="B55" s="7" t="inlineStr"/>
+      <c r="C55" s="7" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" s="5" t="inlineStr">
+      <c r="A56" s="9" t="inlineStr">
         <is>
           <t>implementation_trigger</t>
         </is>
       </c>
-      <c r="B56" s="5" t="inlineStr">
+      <c r="B56" s="9" t="inlineStr">
         <is>
           <t>(?i)(implementation guidance|implementation:|guidelines:|how to implement|supplemental guidance)</t>
         </is>
       </c>
-      <c r="C56" s="6" t="inlineStr">
+      <c r="C56" s="10" t="inlineStr">
         <is>
           <t>Regex for guidance boundary within a control block</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="5" t="inlineStr">
+      <c r="A57" s="9" t="inlineStr">
         <is>
           <t>metadata_scan_paragraphs</t>
         </is>
       </c>
-      <c r="B57" s="5" t="n">
+      <c r="B57" s="9" t="n">
         <v>40</v>
       </c>
-      <c r="C57" s="6" t="inlineStr">
-        <is>
-          <t>How many paragraphs from top of doc to scan for metadata</t>
+      <c r="C57" s="10" t="inlineStr">
+        <is>
+          <t>How many paragraphs from top of doc to scan for metadata [default: 40]</t>
         </is>
       </c>
     </row>
@@ -2110,27 +2805,27 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>Step</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="6" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="6" t="inlineStr">
         <is>
           <t>Script</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="6" t="inlineStr">
         <is>
           <t>Enabled</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="6" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
@@ -2153,7 +2848,7 @@
       <c r="D2" t="b">
         <v>1</v>
       </c>
-      <c r="E2" s="5" t="inlineStr">
+      <c r="E2" s="9" t="inlineStr">
         <is>
           <t>Scan all docs, extract metadata, classify types, score priority, count words</t>
         </is>
@@ -2176,7 +2871,7 @@
       <c r="D3" t="b">
         <v>1</v>
       </c>
-      <c r="E3" s="5" t="inlineStr">
+      <c r="E3" s="9" t="inlineStr">
         <is>
           <t>Scan all docs for acronym candidates and generate audit Excel</t>
         </is>
@@ -2199,7 +2894,7 @@
       <c r="D4" t="b">
         <v>1</v>
       </c>
-      <c r="E4" s="5" t="inlineStr">
+      <c r="E4" s="9" t="inlineStr">
         <is>
           <t>Extract structured control data from compliance docs</t>
         </is>
@@ -2222,7 +2917,7 @@
       <c r="D5" t="b">
         <v>1</v>
       </c>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="E5" s="9" t="inlineStr">
         <is>
           <t>Capture all cross-refs BEFORE any structural changes</t>
         </is>
@@ -2245,7 +2940,7 @@
       <c r="D6" t="b">
         <v>1</v>
       </c>
-      <c r="E6" s="5" t="inlineStr">
+      <c r="E6" s="9" t="inlineStr">
         <is>
           <t>Convert fake bold headings to real Word Heading styles</t>
         </is>
@@ -2268,7 +2963,7 @@
       <c r="D7" t="b">
         <v>1</v>
       </c>
-      <c r="E7" s="5" t="inlineStr">
+      <c r="E7" s="9" t="inlineStr">
         <is>
           <t>Split fixed docs at H1 boundaries into sub-documents</t>
         </is>
@@ -2291,7 +2986,7 @@
       <c r="D8" t="b">
         <v>1</v>
       </c>
-      <c r="E8" s="5" t="inlineStr">
+      <c r="E8" s="9" t="inlineStr">
         <is>
           <t>Add identity metadata to sub-documents</t>
         </is>
@@ -2314,7 +3009,7 @@
       <c r="D9" t="b">
         <v>1</v>
       </c>
-      <c r="E9" s="5" t="inlineStr">
+      <c r="E9" s="9" t="inlineStr">
         <is>
           <t>Convert .docx files to clean Markdown with YAML frontmatter</t>
         </is>
@@ -2337,7 +3032,7 @@
       <c r="D10" t="b">
         <v>1</v>
       </c>
-      <c r="E10" s="5" t="inlineStr">
+      <c r="E10" s="9" t="inlineStr">
         <is>
           <t>Convert .docx files to chunked JSONL for RAG/vector DB ingestion</t>
         </is>
@@ -2360,7 +3055,7 @@
       <c r="D11" t="b">
         <v>1</v>
       </c>
-      <c r="E11" s="5" t="inlineStr">
+      <c r="E11" s="9" t="inlineStr">
         <is>
           <t>Validate all Step 2 controls are present in Step 5 split documents</t>
         </is>
@@ -2383,44 +3078,48 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E32"/>
+  <dimension ref="A1:E36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="65" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="36" customWidth="1" min="2" max="2"/>
     <col width="65" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="4" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="29" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>Setting</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="6" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="6" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
+      <c r="D1" s="6" t="inlineStr"/>
+      <c r="E1" s="6" t="inlineStr"/>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t># General Settings</t>
         </is>
       </c>
-      <c r="B2" s="4" t="inlineStr"/>
-      <c r="C2" s="3" t="inlineStr"/>
+      <c r="B2" s="8" t="inlineStr"/>
+      <c r="C2" s="7" t="inlineStr"/>
+      <c r="D2" s="8" t="inlineStr"/>
+      <c r="E2" s="8" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" s="9" t="inlineStr">
         <is>
           <t>placement</t>
         </is>
@@ -2430,14 +3129,14 @@
           <t>top</t>
         </is>
       </c>
-      <c r="C3" s="6" t="inlineStr">
-        <is>
-          <t>"top", "top_and_bottom", or "each_page"</t>
+      <c r="C3" s="10" t="inlineStr">
+        <is>
+          <t>"top", "top_and_bottom", or "each_page" [default: top]</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" s="9" t="inlineStr">
         <is>
           <t>add_separator</t>
         </is>
@@ -2445,14 +3144,14 @@
       <c r="B4" t="b">
         <v>1</v>
       </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>Horizontal rule after metadata block</t>
+      <c r="C4" s="10" t="inlineStr">
+        <is>
+          <t>Horizontal rule after metadata block [default: TRUE]</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" s="9" t="inlineStr">
         <is>
           <t>font_size</t>
         </is>
@@ -2460,14 +3159,14 @@
       <c r="B5" t="n">
         <v>8</v>
       </c>
-      <c r="C5" s="6" t="inlineStr">
-        <is>
-          <t>Font size (pt) for metadata text</t>
+      <c r="C5" s="10" t="inlineStr">
+        <is>
+          <t>Font size (pt) for metadata text [default: 8]</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="A6" s="9" t="inlineStr">
         <is>
           <t>label_color</t>
         </is>
@@ -2477,32 +3176,52 @@
           <t>2F5496</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>Hex RGB color for metadata labels</t>
+      <c r="C6" s="10" t="inlineStr">
+        <is>
+          <t>Hex RGB color for metadata labels [default: 2F5496]</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="7" t="inlineStr">
         <is>
           <t># Metadata Fields</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr"/>
-      <c r="C7" s="3" t="inlineStr"/>
+      <c r="B7" s="8" t="inlineStr"/>
+      <c r="C7" s="7" t="inlineStr"/>
+      <c r="D7" s="8" t="inlineStr"/>
+      <c r="E7" s="8" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t>## Key | Label | Enabled | Source | Value (for static source)</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" s="5" t="inlineStr"/>
+      <c r="A8" s="10" t="inlineStr">
+        <is>
+          <t>## Key</t>
+        </is>
+      </c>
+      <c r="B8" s="11" t="inlineStr">
+        <is>
+          <t>Label</t>
+        </is>
+      </c>
+      <c r="C8" s="10" t="inlineStr">
+        <is>
+          <t>Enabled</t>
+        </is>
+      </c>
+      <c r="D8" s="11" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="E8" s="11" t="inlineStr">
+        <is>
+          <t>Value (for static source)</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="A9" s="9" t="inlineStr">
         <is>
           <t>name</t>
         </is>
@@ -2512,7 +3231,7 @@
           <t>Document</t>
         </is>
       </c>
-      <c r="C9" s="5" t="b">
+      <c r="C9" s="9" t="b">
         <v>1</v>
       </c>
       <c r="D9" t="inlineStr">
@@ -2523,7 +3242,7 @@
       <c r="E9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="A10" s="9" t="inlineStr">
         <is>
           <t>url</t>
         </is>
@@ -2533,7 +3252,7 @@
           <t>URL</t>
         </is>
       </c>
-      <c r="C10" s="5" t="b">
+      <c r="C10" s="9" t="b">
         <v>1</v>
       </c>
       <c r="D10" t="inlineStr">
@@ -2544,7 +3263,7 @@
       <c r="E10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="A11" s="9" t="inlineStr">
         <is>
           <t>scope</t>
         </is>
@@ -2554,7 +3273,7 @@
           <t>Scope</t>
         </is>
       </c>
-      <c r="C11" s="5" t="b">
+      <c r="C11" s="9" t="b">
         <v>1</v>
       </c>
       <c r="D11" t="inlineStr">
@@ -2565,7 +3284,7 @@
       <c r="E11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="inlineStr">
+      <c r="A12" s="9" t="inlineStr">
         <is>
           <t>intent</t>
         </is>
@@ -2575,7 +3294,7 @@
           <t>Intent</t>
         </is>
       </c>
-      <c r="C12" s="5" t="b">
+      <c r="C12" s="9" t="b">
         <v>1</v>
       </c>
       <c r="D12" t="inlineStr">
@@ -2586,7 +3305,7 @@
       <c r="E12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="inlineStr">
+      <c r="A13" s="9" t="inlineStr">
         <is>
           <t>tags</t>
         </is>
@@ -2596,7 +3315,7 @@
           <t>Tags</t>
         </is>
       </c>
-      <c r="C13" s="5" t="b">
+      <c r="C13" s="9" t="b">
         <v>1</v>
       </c>
       <c r="D13" t="inlineStr">
@@ -2607,234 +3326,302 @@
       <c r="E13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+      <c r="A14" s="9" t="inlineStr">
+        <is>
+          <t>acronyms</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Acronyms</t>
+        </is>
+      </c>
+      <c r="C14" s="9" t="b">
+        <v>1</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="inlineStr">
         <is>
           <t># URL Resolution</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr"/>
-      <c r="C14" s="3" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="B15" s="8" t="inlineStr"/>
+      <c r="C15" s="7" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="9" t="inlineStr">
         <is>
           <t>url.lookup_file</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>./input/Doc_URL.xlsx</t>
         </is>
       </c>
-      <c r="C15" s="6" t="inlineStr">
-        <is>
-          <t>Excel file mapping document names to URLs</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="5" t="inlineStr">
+      <c r="C16" s="10" t="inlineStr">
+        <is>
+          <t>Excel file mapping document names to URLs [default: ./input/Doc_URL.xlsx]</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="9" t="inlineStr">
         <is>
           <t>url.name_column</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>Document_Name</t>
         </is>
       </c>
-      <c r="C16" s="6" t="inlineStr">
-        <is>
-          <t>Column header for doc names in lookup file</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="5" t="inlineStr">
+      <c r="C17" s="10" t="inlineStr">
+        <is>
+          <t>Column header for doc names in lookup file [default: Document_Name]</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="9" t="inlineStr">
         <is>
           <t>url.url_column</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>URL</t>
         </is>
       </c>
-      <c r="C17" s="6" t="inlineStr">
-        <is>
-          <t>Column header for URLs in lookup file</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="5" t="inlineStr">
+      <c r="C18" s="10" t="inlineStr">
+        <is>
+          <t>Column header for URLs in lookup file [default: URL]</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="9" t="inlineStr">
         <is>
           <t>url.sheet</t>
         </is>
       </c>
-      <c r="B18" t="n">
+      <c r="B19" t="n">
         <v>0</v>
       </c>
-      <c r="C18" s="6" t="inlineStr">
-        <is>
-          <t>Sheet name (text) or index (0 = first)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
+      <c r="C19" s="10" t="inlineStr">
+        <is>
+          <t>Sheet name (text) or index (0 = first) [default: 0]</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="9" t="inlineStr">
         <is>
           <t>url.fallback_template</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr"/>
-      <c r="C19" s="6" t="inlineStr">
-        <is>
-          <t>URL template when no Excel match. Use {filename} placeholder</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="3" t="inlineStr">
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" s="10" t="inlineStr">
+        <is>
+          <t>URL template when no Excel match. Use {filename} placeholder [default: empty]</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
         <is>
           <t># Advanced Settings</t>
         </is>
       </c>
-      <c r="B20" s="4" t="inlineStr"/>
-      <c r="C20" s="3" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="5" t="inlineStr">
+      <c r="B21" s="8" t="inlineStr"/>
+      <c r="C21" s="7" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="9" t="inlineStr">
         <is>
           <t>max_scope_chars</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>300</v>
-      </c>
-      <c r="C21" s="6" t="inlineStr">
-        <is>
-          <t>Max chars for scope text extraction</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>max_intent_chars</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>300</v>
       </c>
-      <c r="C22" s="6" t="inlineStr">
-        <is>
-          <t>Max chars for intent text extraction</t>
+      <c r="C22" s="10" t="inlineStr">
+        <is>
+          <t>Max chars for scope text extraction [default: 300]</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="inlineStr">
+      <c r="A23" s="9" t="inlineStr">
+        <is>
+          <t>max_intent_chars</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>300</v>
+      </c>
+      <c r="C23" s="10" t="inlineStr">
+        <is>
+          <t>Max chars for intent text extraction [default: 300]</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
         <is>
           <t># Tag Generation</t>
         </is>
       </c>
-      <c r="B23" s="4" t="inlineStr"/>
-      <c r="C23" s="3" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="5" t="inlineStr">
+      <c r="B24" s="8" t="inlineStr"/>
+      <c r="C24" s="7" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="9" t="inlineStr">
         <is>
           <t>tags.include_doc_type</t>
-        </is>
-      </c>
-      <c r="B24" t="b">
-        <v>1</v>
-      </c>
-      <c r="C24" s="6" t="inlineStr">
-        <is>
-          <t>Add "Type-B" etc. from profiler</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>tags.include_sections_found</t>
         </is>
       </c>
       <c r="B25" t="b">
         <v>1</v>
       </c>
-      <c r="C25" s="6" t="inlineStr">
-        <is>
-          <t>Add "has-scope", "has-controls" etc.</t>
+      <c r="C25" s="10" t="inlineStr">
+        <is>
+          <t>Add "Type-B" etc. from profiler [default: TRUE]</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="5" t="inlineStr">
+      <c r="A26" s="9" t="inlineStr">
+        <is>
+          <t>tags.include_sections_found</t>
+        </is>
+      </c>
+      <c r="B26" t="b">
+        <v>1</v>
+      </c>
+      <c r="C26" s="10" t="inlineStr">
+        <is>
+          <t>Add "has-scope", "has-controls" etc. [default: TRUE]</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="9" t="inlineStr">
+        <is>
+          <t>tags.acronym_definitions_file</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>./input/Acronym_Definitions.xlsx</t>
+        </is>
+      </c>
+      <c r="C27" s="10" t="inlineStr">
+        <is>
+          <t>Path to verified Acronym Definitions Excel (preferred). Leave empty to fall back to acronym_audit_file [default: ./input/Acronym_Definitions.xlsx]</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="9" t="inlineStr">
         <is>
           <t>tags.acronym_audit_file</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr"/>
-      <c r="C26" s="6" t="inlineStr">
-        <is>
-          <t>Path to Acronym Finder output Excel (leave empty to skip)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="5" t="inlineStr">
+      <c r="B28" t="inlineStr"/>
+      <c r="C28" s="10" t="inlineStr">
+        <is>
+          <t>Path to raw Acronym Finder output Excel (fallback if no definitions file). Leave empty to skip [default: empty]</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="9" t="inlineStr">
         <is>
           <t>tags.max_acronym_tags</t>
         </is>
       </c>
-      <c r="B27" t="n">
+      <c r="B29" t="n">
         <v>15</v>
       </c>
-      <c r="C27" s="6" t="inlineStr">
-        <is>
-          <t>Most-frequent first. 0 = unlimited</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="3" t="inlineStr">
+      <c r="C29" s="10" t="inlineStr">
+        <is>
+          <t>Max unique-acronym tags per doc. 0 = unlimited [default: 15]</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="9" t="inlineStr">
+        <is>
+          <t>tags.max_tag_doc_count</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>3</v>
+      </c>
+      <c r="C30" s="10" t="inlineStr">
+        <is>
+          <t>Uniqueness threshold: acronyms in ≤ N docs become tags [default: 3]</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="9" t="inlineStr">
+        <is>
+          <t>tags.max_acronym_definitions</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>0</v>
+      </c>
+      <c r="C31" s="10" t="inlineStr">
+        <is>
+          <t>Max acronym=definition pairs in Acronyms field. 0 = unlimited [default: 0]</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="7" t="inlineStr">
         <is>
           <t># Static Tags</t>
         </is>
       </c>
-      <c r="B28" s="4" t="inlineStr"/>
-      <c r="C28" s="3" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="6" t="inlineStr">
+      <c r="B32" s="8" t="inlineStr"/>
+      <c r="C32" s="7" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="10" t="inlineStr">
         <is>
           <t>## Tags added to ALL documents (one per row, e.g. "InfoSec", "GCC-High")</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr"/>
-      <c r="C29" s="5" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="5" t="inlineStr"/>
-      <c r="B30" t="inlineStr"/>
-      <c r="C30" s="5" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="5" t="inlineStr"/>
-      <c r="B31" t="inlineStr"/>
-      <c r="C31" s="5" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="5" t="inlineStr"/>
-      <c r="B32" t="inlineStr"/>
-      <c r="C32" s="5" t="inlineStr"/>
+      <c r="B33" t="inlineStr"/>
+      <c r="C33" s="9" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="9" t="inlineStr"/>
+      <c r="B34" t="inlineStr"/>
+      <c r="C34" s="9" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="9" t="inlineStr"/>
+      <c r="B35" t="inlineStr"/>
+      <c r="C35" s="9" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="9" t="inlineStr"/>
+      <c r="B36" t="inlineStr"/>
+      <c r="C36" s="9" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E32"/>
+  <autoFilter ref="A1:E36"/>
   <dataValidations count="4">
     <dataValidation sqref="B3" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="Invalid value" error="Please select one of: top, top_and_bottom, each_page" type="list">
       <formula1>"top,top_and_bottom,each_page"</formula1>
@@ -2842,10 +3629,10 @@
     <dataValidation sqref="B4" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid value" error="Please select TRUE or FALSE" type="list">
       <formula1>"TRUE,FALSE"</formula1>
     </dataValidation>
-    <dataValidation sqref="B24" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid value" error="Please select TRUE or FALSE" type="list">
+    <dataValidation sqref="B25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid value" error="Please select TRUE or FALSE" type="list">
       <formula1>"TRUE,FALSE"</formula1>
     </dataValidation>
-    <dataValidation sqref="B25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid value" error="Please select TRUE or FALSE" type="list">
+    <dataValidation sqref="B26" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid value" error="Please select TRUE or FALSE" type="list">
       <formula1>"TRUE,FALSE"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2863,35 +3650,35 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="47" customWidth="1" min="1" max="1"/>
-    <col width="44" customWidth="1" min="2" max="2"/>
+    <col width="65" customWidth="1" min="2" max="2"/>
     <col width="65" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>Setting</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="6" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="6" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="8" t="inlineStr">
         <is>
           <t># Input Mode</t>
         </is>
       </c>
-      <c r="B2" s="4" t="inlineStr"/>
-      <c r="C2" s="3" t="inlineStr"/>
+      <c r="B2" s="7" t="inlineStr"/>
+      <c r="C2" s="7" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2899,12 +3686,12 @@
           <t>pure_conversion</t>
         </is>
       </c>
-      <c r="B3" t="b">
+      <c r="B3" s="9" t="b">
         <v>0</v>
       </c>
-      <c r="C3" s="6" t="inlineStr">
-        <is>
-          <t>TRUE = Pure Conversion (read from input/), FALSE = Optimized (read from step output)</t>
+      <c r="C3" s="10" t="inlineStr">
+        <is>
+          <t>TRUE = Pure Conversion (read from input/), FALSE = Optimized (read from step output) [default: FALSE]</t>
         </is>
       </c>
     </row>
@@ -2914,25 +3701,25 @@
           <t>optimized_source_step</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="9" t="inlineStr">
         <is>
           <t>heading_fixes</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>Step output to read when not pure: "heading_fixes", "split_documents", "metadata"</t>
+      <c r="C4" s="10" t="inlineStr">
+        <is>
+          <t>Step output to read when not pure: "heading_fixes", "split_documents", "metadata" [default: heading_fixes]</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="8" t="inlineStr">
         <is>
           <t># Output</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr"/>
-      <c r="C5" s="3" t="inlineStr"/>
+      <c r="B5" s="7" t="inlineStr"/>
+      <c r="C5" s="7" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2940,25 +3727,25 @@
           <t>output_directory</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="9" t="inlineStr">
         <is>
           <t>./output/7 - markdown</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>Where converted .md files are written</t>
+      <c r="C6" s="10" t="inlineStr">
+        <is>
+          <t>Where converted .md files are written [default: ./output/7 - markdown]</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t># Image Handling</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr"/>
-      <c r="C7" s="3" t="inlineStr"/>
+      <c r="B7" s="7" t="inlineStr"/>
+      <c r="C7" s="7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2966,14 +3753,14 @@
           <t>image_handling</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="9" t="inlineStr">
         <is>
           <t>extract</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>"extract", "placeholder", or "skip"</t>
+      <c r="C8" s="10" t="inlineStr">
+        <is>
+          <t>"extract", "placeholder", or "skip" [default: extract]</t>
         </is>
       </c>
     </row>
@@ -2983,25 +3770,25 @@
           <t>image_subfolder</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="9" t="inlineStr">
         <is>
           <t>images</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>Subfolder name under each doc's image dir</t>
+      <c r="C9" s="10" t="inlineStr">
+        <is>
+          <t>Subfolder name under each doc's image dir [default: images]</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" s="8" t="inlineStr">
         <is>
           <t># Table Conversion</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr"/>
-      <c r="C10" s="3" t="inlineStr"/>
+      <c r="B10" s="7" t="inlineStr"/>
+      <c r="C10" s="7" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -3009,25 +3796,25 @@
           <t>table_strategy</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="9" t="inlineStr">
         <is>
           <t>auto</t>
         </is>
       </c>
-      <c r="C11" s="6" t="inlineStr">
-        <is>
-          <t>"auto" (recommended), "markdown", or "html"</t>
+      <c r="C11" s="10" t="inlineStr">
+        <is>
+          <t>"auto" (recommended), "markdown", or "html" [default: auto]</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" s="8" t="inlineStr">
         <is>
           <t># Heading &amp; Text Cleanup</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr"/>
-      <c r="C12" s="3" t="inlineStr"/>
+      <c r="B12" s="7" t="inlineStr"/>
+      <c r="C12" s="7" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -3035,12 +3822,12 @@
           <t>heading_normalization</t>
         </is>
       </c>
-      <c r="B13" t="b">
+      <c r="B13" s="9" t="b">
         <v>1</v>
       </c>
-      <c r="C13" s="6" t="inlineStr">
-        <is>
-          <t>Shift heading levels so doc starts at H1</t>
+      <c r="C13" s="10" t="inlineStr">
+        <is>
+          <t>Shift heading levels so doc starts at H1 [default: TRUE]</t>
         </is>
       </c>
     </row>
@@ -3050,12 +3837,12 @@
           <t>max_heading_level</t>
         </is>
       </c>
-      <c r="B14" t="n">
+      <c r="B14" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="C14" s="6" t="inlineStr">
-        <is>
-          <t>Max heading depth in output (2 = only H1/H2). H3+ collapsed to this level.</t>
+      <c r="C14" s="10" t="inlineStr">
+        <is>
+          <t>Max heading depth in output (2 = only H1/H2). H3+ collapsed to this level. [default: 2]</t>
         </is>
       </c>
     </row>
@@ -3065,12 +3852,12 @@
           <t>max_consecutive_blank_lines</t>
         </is>
       </c>
-      <c r="B15" t="n">
+      <c r="B15" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="C15" s="6" t="inlineStr">
-        <is>
-          <t>Collapse runs of blank lines</t>
+      <c r="C15" s="10" t="inlineStr">
+        <is>
+          <t>Collapse runs of blank lines [default: 2]</t>
         </is>
       </c>
     </row>
@@ -3080,12 +3867,12 @@
           <t>clean_smart_quotes</t>
         </is>
       </c>
-      <c r="B16" t="b">
+      <c r="B16" s="9" t="b">
         <v>1</v>
       </c>
-      <c r="C16" s="6" t="inlineStr">
-        <is>
-          <t>Convert smart quotes to ASCII</t>
+      <c r="C16" s="10" t="inlineStr">
+        <is>
+          <t>Convert smart quotes to ASCII [default: TRUE]</t>
         </is>
       </c>
     </row>
@@ -3095,12 +3882,12 @@
           <t>strip_zero_width_chars</t>
         </is>
       </c>
-      <c r="B17" t="b">
+      <c r="B17" s="9" t="b">
         <v>1</v>
       </c>
-      <c r="C17" s="6" t="inlineStr">
-        <is>
-          <t>Remove zero-width spaces, BOM, etc.</t>
+      <c r="C17" s="10" t="inlineStr">
+        <is>
+          <t>Remove zero-width spaces, BOM, etc. [default: TRUE]</t>
         </is>
       </c>
     </row>
@@ -3110,23 +3897,23 @@
           <t>extract_text_boxes</t>
         </is>
       </c>
-      <c r="B18" t="b">
+      <c r="B18" s="9" t="b">
         <v>1</v>
       </c>
-      <c r="C18" s="6" t="inlineStr">
-        <is>
-          <t>Extract floating text box content inline</t>
+      <c r="C18" s="10" t="inlineStr">
+        <is>
+          <t>Extract floating text box content inline [default: TRUE]</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="inlineStr">
+      <c r="A19" s="8" t="inlineStr">
         <is>
           <t># Doc URL Resolution</t>
         </is>
       </c>
-      <c r="B19" s="4" t="inlineStr"/>
-      <c r="C19" s="3" t="inlineStr"/>
+      <c r="B19" s="7" t="inlineStr"/>
+      <c r="C19" s="7" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -3134,23 +3921,23 @@
           <t>include_doc_url</t>
         </is>
       </c>
-      <c r="B20" t="b">
+      <c r="B20" s="9" t="b">
         <v>1</v>
       </c>
-      <c r="C20" s="6" t="inlineStr">
-        <is>
-          <t>Resolve Doc URLs from metadata.url Excel lookup into frontmatter</t>
+      <c r="C20" s="10" t="inlineStr">
+        <is>
+          <t>Resolve Doc URLs from metadata.url Excel lookup into frontmatter [default: TRUE]</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="inlineStr">
+      <c r="A21" s="8" t="inlineStr">
         <is>
           <t># Metadata Placement</t>
         </is>
       </c>
-      <c r="B21" s="4" t="inlineStr"/>
-      <c r="C21" s="3" t="inlineStr"/>
+      <c r="B21" s="7" t="inlineStr"/>
+      <c r="C21" s="7" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -3158,25 +3945,25 @@
           <t>metadata_placement</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B22" s="9" t="inlineStr">
         <is>
           <t>top</t>
         </is>
       </c>
-      <c r="C22" s="6" t="inlineStr">
-        <is>
-          <t>"top" = YAML frontmatter only; "top_and_bottom" = also append readable block at end</t>
+      <c r="C22" s="10" t="inlineStr">
+        <is>
+          <t>"top" = YAML frontmatter only; "top_and_bottom" = also append readable block at end [default: top]</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="4" t="inlineStr">
+      <c r="A23" s="8" t="inlineStr">
         <is>
           <t># Control ID Headings</t>
         </is>
       </c>
-      <c r="B23" s="4" t="inlineStr"/>
-      <c r="C23" s="3" t="inlineStr"/>
+      <c r="B23" s="7" t="inlineStr"/>
+      <c r="C23" s="7" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -3184,23 +3971,23 @@
           <t>promote_control_ids_to_heading</t>
         </is>
       </c>
-      <c r="B24" t="b">
+      <c r="B24" s="9" t="b">
         <v>1</v>
       </c>
-      <c r="C24" s="6" t="inlineStr">
-        <is>
-          <t>Promote paragraphs with control IDs to H2 headings (uses control_extraction patterns)</t>
+      <c r="C24" s="10" t="inlineStr">
+        <is>
+          <t>Promote paragraphs with control IDs to H2 headings (uses control_extraction patterns) [default: TRUE]</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="4" t="inlineStr">
+      <c r="A25" s="8" t="inlineStr">
         <is>
           <t># Logging</t>
         </is>
       </c>
-      <c r="B25" s="4" t="inlineStr"/>
-      <c r="C25" s="3" t="inlineStr"/>
+      <c r="B25" s="7" t="inlineStr"/>
+      <c r="C25" s="7" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -3208,25 +3995,25 @@
           <t>log_file_prefix</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B26" s="9" t="inlineStr">
         <is>
           <t>docx2md_log</t>
         </is>
       </c>
-      <c r="C26" s="6" t="inlineStr">
-        <is>
-          <t>Prefix for timestamped log Excel file</t>
+      <c r="C26" s="10" t="inlineStr">
+        <is>
+          <t>Prefix for timestamped log Excel file [default: docx2md_log]</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="4" t="inlineStr">
+      <c r="A27" s="8" t="inlineStr">
         <is>
           <t># Metadata Frontmatter</t>
         </is>
       </c>
-      <c r="B27" s="4" t="inlineStr"/>
-      <c r="C27" s="3" t="inlineStr"/>
+      <c r="B27" s="7" t="inlineStr"/>
+      <c r="C27" s="7" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -3234,23 +4021,23 @@
           <t>include_metadata_frontmatter</t>
         </is>
       </c>
-      <c r="B28" t="b">
+      <c r="B28" s="9" t="b">
         <v>1</v>
       </c>
-      <c r="C28" s="6" t="inlineStr">
-        <is>
-          <t>Add YAML frontmatter block at top of each .md file</t>
+      <c r="C28" s="10" t="inlineStr">
+        <is>
+          <t>Add YAML frontmatter block at top of each .md file [default: TRUE]</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="7" t="inlineStr">
+      <c r="A29" s="11" t="inlineStr">
         <is>
           <t>## Metadata fields: Name | Source | Default</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr"/>
-      <c r="C29" s="5" t="inlineStr"/>
+      <c r="B29" s="9" t="inlineStr"/>
+      <c r="C29" s="9" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -3258,12 +4045,12 @@
           <t>title</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B30" s="9" t="inlineStr">
         <is>
           <t>core:title</t>
         </is>
       </c>
-      <c r="C30" s="5" t="inlineStr"/>
+      <c r="C30" s="9" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -3271,81 +4058,77 @@
           <t>source_file</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B31" s="9" t="inlineStr">
         <is>
           <t>filename</t>
         </is>
       </c>
-      <c r="C31" s="5" t="inlineStr"/>
+      <c r="C31" s="9" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>author</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>core:author</t>
-        </is>
-      </c>
-      <c r="C32" s="5" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="B32" s="9" t="inlineStr">
+        <is>
+          <t>core:modified</t>
+        </is>
+      </c>
+      <c r="C32" s="9" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>created</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>core:created</t>
-        </is>
-      </c>
-      <c r="C33" s="5" t="inlineStr"/>
+          <t>doc_id</t>
+        </is>
+      </c>
+      <c r="B33" s="9" t="inlineStr">
+        <is>
+          <t>filename_regex:([A-Z]+-[A-Z]+-\d{4}-\d+)</t>
+        </is>
+      </c>
+      <c r="C33" s="9" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>modified</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>core:modified</t>
-        </is>
-      </c>
-      <c r="C34" s="5" t="inlineStr"/>
+          <t>converted</t>
+        </is>
+      </c>
+      <c r="B34" s="9" t="inlineStr">
+        <is>
+          <t>converted_date</t>
+        </is>
+      </c>
+      <c r="C34" s="9" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>doc_id</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>filename_regex:([A-Z]+-[A-Z]+-\d{4}-\d+)</t>
-        </is>
-      </c>
-      <c r="C35" s="5" t="inlineStr"/>
+          <t>PublishedURL</t>
+        </is>
+      </c>
+      <c r="B35" s="9" t="inlineStr">
+        <is>
+          <t>doc_url</t>
+        </is>
+      </c>
+      <c r="C35" s="9" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>converted</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>converted_date</t>
-        </is>
-      </c>
-      <c r="C36" s="5" t="inlineStr"/>
+          <t>Acronyms</t>
+        </is>
+      </c>
+      <c r="B36" s="9" t="inlineStr">
+        <is>
+          <t>excel_lookup_dict:./input/Acronym_Definitions.xlsx:Acronym Definitions:Document:Acronym:Definition</t>
+        </is>
+      </c>
+      <c r="C36" s="9" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:C36"/>
@@ -3403,30 +4186,30 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>Setting</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="6" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="6" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="8" t="inlineStr">
         <is>
           <t># Input Mode</t>
         </is>
       </c>
-      <c r="B2" s="4" t="inlineStr"/>
-      <c r="C2" s="3" t="inlineStr"/>
+      <c r="B2" s="8" t="inlineStr"/>
+      <c r="C2" s="7" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -3437,9 +4220,9 @@
       <c r="B3" t="b">
         <v>0</v>
       </c>
-      <c r="C3" s="6" t="inlineStr">
-        <is>
-          <t>TRUE = Pure Conversion (read from input/), FALSE = Optimized (read from step output)</t>
+      <c r="C3" s="10" t="inlineStr">
+        <is>
+          <t>TRUE = Pure Conversion (read from input/), FALSE = Optimized (read from step output) [default: FALSE]</t>
         </is>
       </c>
     </row>
@@ -3454,20 +4237,20 @@
           <t>heading_fixes</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>Step output to read when not pure: "heading_fixes", "split_documents", "metadata"</t>
+      <c r="C4" s="10" t="inlineStr">
+        <is>
+          <t>Step output to read when not pure: "heading_fixes", "split_documents", "metadata" [default: heading_fixes]</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="8" t="inlineStr">
         <is>
           <t># Output</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr"/>
-      <c r="C5" s="3" t="inlineStr"/>
+      <c r="B5" s="8" t="inlineStr"/>
+      <c r="C5" s="7" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -3480,20 +4263,20 @@
           <t>./output/8 - jsonl</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>Where converted .jsonl.txt files are written</t>
+      <c r="C6" s="10" t="inlineStr">
+        <is>
+          <t>Where converted .jsonl.txt files are written [default: ./output/8 - jsonl]</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t># Chunking</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr"/>
-      <c r="C7" s="3" t="inlineStr"/>
+      <c r="B7" s="8" t="inlineStr"/>
+      <c r="C7" s="7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -3504,9 +4287,9 @@
       <c r="B8" t="n">
         <v>1500</v>
       </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>Maximum characters per chunk</t>
+      <c r="C8" s="10" t="inlineStr">
+        <is>
+          <t>Maximum characters per chunk [default: 1500]</t>
         </is>
       </c>
     </row>
@@ -3519,9 +4302,9 @@
       <c r="B9" t="n">
         <v>30</v>
       </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>Words to overlap between consecutive chunks</t>
+      <c r="C9" s="10" t="inlineStr">
+        <is>
+          <t>Words to overlap between consecutive chunks [default: 30]</t>
         </is>
       </c>
     </row>
@@ -3534,20 +4317,20 @@
       <c r="B10" t="n">
         <v>100</v>
       </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>Merge trailing chunks smaller than this into previous</t>
+      <c r="C10" s="10" t="inlineStr">
+        <is>
+          <t>Merge trailing chunks smaller than this into previous [default: 100]</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="8" t="inlineStr">
         <is>
           <t># Acronym Definitions</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr"/>
-      <c r="C11" s="3" t="inlineStr"/>
+      <c r="B11" s="8" t="inlineStr"/>
+      <c r="C11" s="7" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -3560,20 +4343,20 @@
           <t>./input/Acronym_Definitions.xlsx</t>
         </is>
       </c>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t>Path to confirmed acronym definitions Excel (Per Document sheet)</t>
+      <c r="C12" s="10" t="inlineStr">
+        <is>
+          <t>Path to confirmed acronym definitions Excel (Per Document sheet) [default: ./input/Acronym_Definitions.xlsx]</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="A13" s="8" t="inlineStr">
         <is>
           <t># Tag Mapping</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr"/>
-      <c r="C13" s="3" t="inlineStr"/>
+      <c r="B13" s="8" t="inlineStr"/>
+      <c r="C13" s="7" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -3582,9 +4365,9 @@
         </is>
       </c>
       <c r="B14" t="inlineStr"/>
-      <c r="C14" s="6" t="inlineStr">
-        <is>
-          <t>Optional Excel file mapping documents to tags (leave empty to skip)</t>
+      <c r="C14" s="10" t="inlineStr">
+        <is>
+          <t>Optional Excel file mapping documents to tags (leave empty to skip) [default: empty]</t>
         </is>
       </c>
     </row>
@@ -3605,7 +4388,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C24"/>
+  <dimension ref="A1:C99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -3614,30 +4397,30 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>Setting</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="6" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="6" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="8" t="inlineStr">
         <is>
           <t># Output</t>
         </is>
       </c>
-      <c r="B2" s="4" t="inlineStr"/>
-      <c r="C2" s="3" t="inlineStr"/>
+      <c r="B2" s="8" t="inlineStr"/>
+      <c r="C2" s="7" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -3650,20 +4433,20 @@
           <t>acronym_audit.xlsx</t>
         </is>
       </c>
-      <c r="C3" s="6" t="inlineStr">
-        <is>
-          <t>Filename for the audit Excel report</t>
+      <c r="C3" s="10" t="inlineStr">
+        <is>
+          <t>Filename for the audit Excel report [default: acronym_audit.xlsx]</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="8" t="inlineStr">
         <is>
           <t># Search Settings</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr"/>
-      <c r="C4" s="3" t="inlineStr"/>
+      <c r="B4" s="8" t="inlineStr"/>
+      <c r="C4" s="7" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -3674,9 +4457,9 @@
       <c r="B5" t="n">
         <v>2</v>
       </c>
-      <c r="C5" s="6" t="inlineStr">
-        <is>
-          <t>Minimum acronym length (2 = 'AC')</t>
+      <c r="C5" s="10" t="inlineStr">
+        <is>
+          <t>Minimum acronym length (2 = 'AC') [default: 2]</t>
         </is>
       </c>
     </row>
@@ -3689,9 +4472,9 @@
       <c r="B6" t="n">
         <v>8</v>
       </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>Maximum acronym length</t>
+      <c r="C6" s="10" t="inlineStr">
+        <is>
+          <t>Maximum acronym length [default: 8]</t>
         </is>
       </c>
     </row>
@@ -3704,9 +4487,9 @@
       <c r="B7" t="b">
         <v>1</v>
       </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>Include acronyms found inside tables</t>
+      <c r="C7" s="10" t="inlineStr">
+        <is>
+          <t>Include acronyms found inside tables [default: TRUE]</t>
         </is>
       </c>
     </row>
@@ -3719,9 +4502,9 @@
       <c r="B8" t="b">
         <v>1</v>
       </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>Include acronyms found in headers/footers</t>
+      <c r="C8" s="10" t="inlineStr">
+        <is>
+          <t>Include acronyms found in headers/footers [default: TRUE]</t>
         </is>
       </c>
     </row>
@@ -3734,9 +4517,9 @@
       <c r="B9" t="b">
         <v>1</v>
       </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>Include acronyms found in text boxes</t>
+      <c r="C9" s="10" t="inlineStr">
+        <is>
+          <t>Include acronyms found in text boxes [default: TRUE]</t>
         </is>
       </c>
     </row>
@@ -3749,9 +4532,9 @@
       <c r="B10" t="n">
         <v>1</v>
       </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>Min occurrences across ALL docs to appear in results</t>
+      <c r="C10" s="10" t="inlineStr">
+        <is>
+          <t>Min occurrences across ALL docs to appear in results [default: 1]</t>
         </is>
       </c>
     </row>
@@ -3764,20 +4547,20 @@
       <c r="B11" t="n">
         <v>1</v>
       </c>
-      <c r="C11" s="6" t="inlineStr">
-        <is>
-          <t>Min occurrences within a single doc to appear</t>
+      <c r="C11" s="10" t="inlineStr">
+        <is>
+          <t>Min occurrences within a single doc to appear [default: 1]</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" s="8" t="inlineStr">
         <is>
           <t># Detection Patterns</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr"/>
-      <c r="C12" s="3" t="inlineStr"/>
+      <c r="B12" s="8" t="inlineStr"/>
+      <c r="C12" s="7" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -3788,9 +4571,9 @@
       <c r="B13" t="b">
         <v>1</v>
       </c>
-      <c r="C13" s="6" t="inlineStr">
-        <is>
-          <t>ABC, NIST, GCC</t>
+      <c r="C13" s="10" t="inlineStr">
+        <is>
+          <t>ABC, NIST, GCC [default: TRUE]</t>
         </is>
       </c>
     </row>
@@ -3803,9 +4586,9 @@
       <c r="B14" t="b">
         <v>1</v>
       </c>
-      <c r="C14" s="6" t="inlineStr">
-        <is>
-          <t>AC-2, 800-53</t>
+      <c r="C14" s="10" t="inlineStr">
+        <is>
+          <t>AC-2, 800-53 [default: TRUE]</t>
         </is>
       </c>
     </row>
@@ -3818,9 +4601,9 @@
       <c r="B15" t="b">
         <v>1</v>
       </c>
-      <c r="C15" s="6" t="inlineStr">
-        <is>
-          <t>FedRAMP, ATO-P</t>
+      <c r="C15" s="10" t="inlineStr">
+        <is>
+          <t>FedRAMP, ATO-P [default: TRUE]</t>
         </is>
       </c>
     </row>
@@ -3833,9 +4616,9 @@
       <c r="B16" t="b">
         <v>1</v>
       </c>
-      <c r="C16" s="6" t="inlineStr">
-        <is>
-          <t>IT/OT, CI/CD</t>
+      <c r="C16" s="10" t="inlineStr">
+        <is>
+          <t>IT/OT, CI/CD [default: TRUE]</t>
         </is>
       </c>
     </row>
@@ -3848,57 +4631,732 @@
       <c r="B17" t="b">
         <v>1</v>
       </c>
-      <c r="C17" s="6" t="inlineStr">
-        <is>
-          <t>"Multi-Factor Authentication (MFA)"</t>
+      <c r="C17" s="10" t="inlineStr">
+        <is>
+          <t>"Multi-Factor Authentication (MFA)" [default: TRUE]</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="inlineStr">
+      <c r="A18" s="8" t="inlineStr">
         <is>
           <t># Ignore List (one per row)</t>
         </is>
       </c>
-      <c r="B18" s="4" t="inlineStr"/>
-      <c r="C18" s="3" t="inlineStr"/>
+      <c r="B18" s="8" t="inlineStr"/>
+      <c r="C18" s="7" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="7" t="inlineStr">
+      <c r="A19" s="11" t="inlineStr">
         <is>
           <t>## Acronyms and uppercase words to skip entirely</t>
         </is>
       </c>
       <c r="B19" t="inlineStr"/>
-      <c r="C19" s="5" t="inlineStr"/>
+      <c r="C19" s="9" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr"/>
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>THE</t>
+        </is>
+      </c>
       <c r="B20" t="inlineStr"/>
-      <c r="C20" s="5" t="inlineStr"/>
+      <c r="C20" s="9" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr"/>
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>AND</t>
+        </is>
+      </c>
       <c r="B21" t="inlineStr"/>
-      <c r="C21" s="5" t="inlineStr"/>
+      <c r="C21" s="9" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr"/>
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>FOR</t>
+        </is>
+      </c>
       <c r="B22" t="inlineStr"/>
-      <c r="C22" s="5" t="inlineStr"/>
+      <c r="C22" s="9" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr"/>
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>NOT</t>
+        </is>
+      </c>
       <c r="B23" t="inlineStr"/>
-      <c r="C23" s="5" t="inlineStr"/>
+      <c r="C23" s="9" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr"/>
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>BUT</t>
+        </is>
+      </c>
       <c r="B24" t="inlineStr"/>
-      <c r="C24" s="5" t="inlineStr"/>
+      <c r="C24" s="9" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr"/>
+      <c r="C25" s="9" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>ARE</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr"/>
+      <c r="C26" s="9" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>CAN</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr"/>
+      <c r="C27" s="9" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>HAS</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr"/>
+      <c r="C28" s="9" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>HER</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr"/>
+      <c r="C29" s="9" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>WAS</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr"/>
+      <c r="C30" s="9" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>ONE</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr"/>
+      <c r="C31" s="9" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>OUR</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr"/>
+      <c r="C32" s="9" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr"/>
+      <c r="C33" s="9" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>YOU</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr"/>
+      <c r="C34" s="9" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>USE</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr"/>
+      <c r="C35" s="9" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>MAY</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr"/>
+      <c r="C36" s="9" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>SHALL</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr"/>
+      <c r="C37" s="9" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>MUST</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr"/>
+      <c r="C38" s="9" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>WILL</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr"/>
+      <c r="C39" s="9" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>WITH</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr"/>
+      <c r="C40" s="9" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>THIS</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr"/>
+      <c r="C41" s="9" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>THAT</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr"/>
+      <c r="C42" s="9" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>FROM</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr"/>
+      <c r="C43" s="9" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>THEY</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr"/>
+      <c r="C44" s="9" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>BEEN</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr"/>
+      <c r="C45" s="9" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>HAVE</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr"/>
+      <c r="C46" s="9" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>EACH</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr"/>
+      <c r="C47" s="9" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>MAKE</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr"/>
+      <c r="C48" s="9" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>WHEN</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr"/>
+      <c r="C49" s="9" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>DOES</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr"/>
+      <c r="C50" s="9" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>INTO</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr"/>
+      <c r="C51" s="9" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>THEM</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr"/>
+      <c r="C52" s="9" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>THEN</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr"/>
+      <c r="C53" s="9" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>THAN</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr"/>
+      <c r="C54" s="9" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>ONLY</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr"/>
+      <c r="C55" s="9" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr"/>
+      <c r="C56" s="9" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>SUCH</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr"/>
+      <c r="C57" s="9" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>ALSO</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr"/>
+      <c r="C58" s="9" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>SOME</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr"/>
+      <c r="C59" s="9" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>THESE</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr"/>
+      <c r="C60" s="9" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr"/>
+      <c r="C61" s="9" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>WHICH</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr"/>
+      <c r="C62" s="9" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>THEIR</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr"/>
+      <c r="C63" s="9" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>THERE</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr"/>
+      <c r="C64" s="9" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>WOULD</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr"/>
+      <c r="C65" s="9" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>ABOUT</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr"/>
+      <c r="C66" s="9" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>AFTER</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr"/>
+      <c r="C67" s="9" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>COULD</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr"/>
+      <c r="C68" s="9" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>WHERE</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr"/>
+      <c r="C69" s="9" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>SHOULD</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr"/>
+      <c r="C70" s="9" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>THOSE</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr"/>
+      <c r="C71" s="9" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>II</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr"/>
+      <c r="C72" s="9" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>III</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr"/>
+      <c r="C73" s="9" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>IV</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr"/>
+      <c r="C74" s="9" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr"/>
+      <c r="C75" s="9" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>VII</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr"/>
+      <c r="C76" s="9" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>VIII</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr"/>
+      <c r="C77" s="9" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>IX</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr"/>
+      <c r="C78" s="9" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>XI</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr"/>
+      <c r="C79" s="9" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>XII</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr"/>
+      <c r="C80" s="9" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>PAGE</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr"/>
+      <c r="C81" s="9" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>DATE</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr"/>
+      <c r="C82" s="9" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>DRAFT</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr"/>
+      <c r="C83" s="9" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>FINAL</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr"/>
+      <c r="C84" s="9" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>NOTE</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr"/>
+      <c r="C85" s="9" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>TABLE</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr"/>
+      <c r="C86" s="9" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>FIGURE</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr"/>
+      <c r="C87" s="9" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>REV</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr"/>
+      <c r="C88" s="9" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>VER</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr"/>
+      <c r="C89" s="9" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr"/>
+      <c r="C90" s="9" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr"/>
+      <c r="C91" s="9" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>TODO</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr"/>
+      <c r="C92" s="9" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr"/>
+      <c r="C93" s="9" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr"/>
+      <c r="C94" s="9" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr"/>
+      <c r="B95" t="inlineStr"/>
+      <c r="C95" s="9" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr"/>
+      <c r="B96" t="inlineStr"/>
+      <c r="C96" s="9" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr"/>
+      <c r="B97" t="inlineStr"/>
+      <c r="C97" s="9" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr"/>
+      <c r="B98" t="inlineStr"/>
+      <c r="C98" s="9" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr"/>
+      <c r="B99" t="inlineStr"/>
+      <c r="C99" s="9" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C24"/>
+  <autoFilter ref="A1:C99"/>
   <dataValidations count="8">
     <dataValidation sqref="B7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid value" error="Please select TRUE or FALSE" type="list">
       <formula1>"TRUE,FALSE"</formula1>
@@ -3944,33 +5402,33 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>Setting</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="6" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="6" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t># Directory Settings</t>
         </is>
       </c>
-      <c r="B2" s="4" t="inlineStr"/>
-      <c r="C2" s="3" t="inlineStr"/>
+      <c r="B2" s="8" t="inlineStr"/>
+      <c r="C2" s="7" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" s="9" t="inlineStr">
         <is>
           <t>directory</t>
         </is>
@@ -3980,14 +5438,14 @@
           <t>./input</t>
         </is>
       </c>
-      <c r="C3" s="6" t="inlineStr">
-        <is>
-          <t>Path to folder containing .docx files (absolute or relative)</t>
+      <c r="C3" s="10" t="inlineStr">
+        <is>
+          <t>Path to folder containing .docx files (absolute or relative) [default: ./input]</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" s="9" t="inlineStr">
         <is>
           <t>pattern</t>
         </is>
@@ -3997,14 +5455,14 @@
           <t>*.docx</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>File glob pattern — almost always *.docx</t>
+      <c r="C4" s="10" t="inlineStr">
+        <is>
+          <t>File glob pattern — almost always *.docx [default: *.docx]</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" s="9" t="inlineStr">
         <is>
           <t>recursive</t>
         </is>
@@ -4012,94 +5470,94 @@
       <c r="B5" t="b">
         <v>0</v>
       </c>
-      <c r="C5" s="6" t="inlineStr">
-        <is>
-          <t>Scan sub-folders? TRUE if docs are in sub-folders</t>
+      <c r="C5" s="10" t="inlineStr">
+        <is>
+          <t>Scan sub-folders? TRUE if docs are in sub-folders [default: FALSE]</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t># Exclude Patterns</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr"/>
-      <c r="C6" s="3" t="inlineStr"/>
+      <c r="B6" s="8" t="inlineStr"/>
+      <c r="C6" s="7" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="inlineStr">
-        <is>
-          <t>## Files matching ANY of these patterns are skipped (case-insensitive substring)</t>
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>## Column A = pattern to exclude (one per row). Files matching ANY pattern are skipped</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
-      <c r="C7" s="5" t="inlineStr"/>
+      <c r="C7" s="9" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="A8" s="9" t="inlineStr">
         <is>
           <t>~$</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr">
+      <c r="B8" s="11" t="inlineStr">
         <is>
           <t>Word temp/lock files</t>
         </is>
       </c>
-      <c r="C8" s="5" t="inlineStr"/>
+      <c r="C8" s="9" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="A9" s="9" t="inlineStr">
         <is>
           <t>_optimized</t>
         </is>
       </c>
-      <c r="B9" s="7" t="inlineStr">
+      <c r="B9" s="11" t="inlineStr">
         <is>
           <t>Already-processed files</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr"/>
+      <c r="C9" s="9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="A10" s="9" t="inlineStr">
         <is>
           <t>_backup</t>
         </is>
       </c>
-      <c r="B10" s="7" t="inlineStr">
+      <c r="B10" s="11" t="inlineStr">
         <is>
           <t>Backup copies</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr"/>
+      <c r="C10" s="9" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="A11" s="9" t="inlineStr">
         <is>
           <t>_fixed</t>
         </is>
       </c>
-      <c r="B11" s="7" t="inlineStr">
+      <c r="B11" s="11" t="inlineStr">
         <is>
           <t>Output from heading fixer</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr"/>
+      <c r="C11" s="9" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="inlineStr">
+      <c r="A12" s="9" t="inlineStr">
         <is>
           <t>template</t>
         </is>
       </c>
-      <c r="B12" s="7" t="inlineStr">
+      <c r="B12" s="11" t="inlineStr">
         <is>
           <t>Template files, not actual policies</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr"/>
+      <c r="C12" s="9" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:C12"/>
@@ -4123,34 +5581,34 @@
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="27" customWidth="1" min="2" max="2"/>
-    <col width="47" customWidth="1" min="3" max="3"/>
+    <col width="65" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>Setting</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="6" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="6" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="8" t="inlineStr">
         <is>
           <t># Root Output Directory</t>
         </is>
       </c>
-      <c r="B2" s="4" t="inlineStr"/>
-      <c r="C2" s="4" t="inlineStr"/>
+      <c r="B2" s="8" t="inlineStr"/>
+      <c r="C2" s="7" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -4163,20 +5621,20 @@
           <t>./output</t>
         </is>
       </c>
-      <c r="C3" s="7" t="inlineStr">
-        <is>
-          <t>All step outputs go under this directory</t>
+      <c r="C3" s="10" t="inlineStr">
+        <is>
+          <t>All step outputs go under this directory [default: ./output]</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="8" t="inlineStr">
         <is>
           <t># Step 0 — Profiler</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr"/>
-      <c r="C4" s="4" t="inlineStr"/>
+      <c r="B4" s="8" t="inlineStr"/>
+      <c r="C4" s="7" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -4189,9 +5647,9 @@
           <t>0 - profiler</t>
         </is>
       </c>
-      <c r="C5" s="7" t="inlineStr">
-        <is>
-          <t>Sub-folder name</t>
+      <c r="C5" s="10" t="inlineStr">
+        <is>
+          <t>Sub-folder name [default: 0 - profiler]</t>
         </is>
       </c>
     </row>
@@ -4206,9 +5664,9 @@
           <t>document_inventory.xlsx</t>
         </is>
       </c>
-      <c r="C6" s="7" t="inlineStr">
-        <is>
-          <t>Master spreadsheet</t>
+      <c r="C6" s="10" t="inlineStr">
+        <is>
+          <t>Master spreadsheet [default: document_inventory.xlsx]</t>
         </is>
       </c>
     </row>
@@ -4223,9 +5681,9 @@
           <t>document_profiles.json</t>
         </is>
       </c>
-      <c r="C7" s="7" t="inlineStr">
-        <is>
-          <t>Machine-readable profiles</t>
+      <c r="C7" s="10" t="inlineStr">
+        <is>
+          <t>Machine-readable profiles [default: document_profiles.json]</t>
         </is>
       </c>
     </row>
@@ -4240,9 +5698,9 @@
           <t>section_inventory.csv</t>
         </is>
       </c>
-      <c r="C8" s="7" t="inlineStr">
-        <is>
-          <t>One row per section per doc</t>
+      <c r="C8" s="10" t="inlineStr">
+        <is>
+          <t>One row per section per doc [default: section_inventory.csv]</t>
         </is>
       </c>
     </row>
@@ -4257,9 +5715,9 @@
           <t>table_inventory.csv</t>
         </is>
       </c>
-      <c r="C9" s="7" t="inlineStr">
-        <is>
-          <t>One row per table per doc</t>
+      <c r="C9" s="10" t="inlineStr">
+        <is>
+          <t>One row per table per doc [default: table_inventory.csv]</t>
         </is>
       </c>
     </row>
@@ -4274,20 +5732,20 @@
           <t>crossref_inventory.csv</t>
         </is>
       </c>
-      <c r="C10" s="7" t="inlineStr">
-        <is>
-          <t>One row per cross-reference</t>
+      <c r="C10" s="10" t="inlineStr">
+        <is>
+          <t>One row per cross-reference [default: crossref_inventory.csv]</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="8" t="inlineStr">
         <is>
           <t># Step 1 — Acronyms</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr"/>
-      <c r="C11" s="4" t="inlineStr"/>
+      <c r="B11" s="8" t="inlineStr"/>
+      <c r="C11" s="7" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -4300,9 +5758,9 @@
           <t>1 - acronyms</t>
         </is>
       </c>
-      <c r="C12" s="7" t="inlineStr">
-        <is>
-          <t>Sub-folder name</t>
+      <c r="C12" s="10" t="inlineStr">
+        <is>
+          <t>Sub-folder name [default: 1 - acronyms]</t>
         </is>
       </c>
     </row>
@@ -4317,20 +5775,20 @@
           <t>acronym_audit.xlsx</t>
         </is>
       </c>
-      <c r="C13" s="7" t="inlineStr">
-        <is>
-          <t>Audit Excel output</t>
+      <c r="C13" s="10" t="inlineStr">
+        <is>
+          <t>Audit Excel output [default: acronym_audit.xlsx]</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+      <c r="A14" s="8" t="inlineStr">
         <is>
           <t># Step 2 — Controls</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr"/>
-      <c r="C14" s="4" t="inlineStr"/>
+      <c r="B14" s="8" t="inlineStr"/>
+      <c r="C14" s="7" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -4343,9 +5801,9 @@
           <t>2 - controls</t>
         </is>
       </c>
-      <c r="C15" s="7" t="inlineStr">
-        <is>
-          <t>Sub-folder name</t>
+      <c r="C15" s="10" t="inlineStr">
+        <is>
+          <t>Sub-folder name [default: 2 - controls]</t>
         </is>
       </c>
     </row>
@@ -4360,9 +5818,9 @@
           <t>controls_output.csv</t>
         </is>
       </c>
-      <c r="C16" s="7" t="inlineStr">
-        <is>
-          <t>CSV output</t>
+      <c r="C16" s="10" t="inlineStr">
+        <is>
+          <t>CSV output [default: controls_output.csv]</t>
         </is>
       </c>
     </row>
@@ -4377,9 +5835,9 @@
           <t>controls_output.xlsx</t>
         </is>
       </c>
-      <c r="C17" s="7" t="inlineStr">
-        <is>
-          <t>Excel output</t>
+      <c r="C17" s="10" t="inlineStr">
+        <is>
+          <t>Excel output [default: controls_output.xlsx]</t>
         </is>
       </c>
     </row>
@@ -4394,9 +5852,9 @@
           <t>checkpoint.json</t>
         </is>
       </c>
-      <c r="C18" s="7" t="inlineStr">
-        <is>
-          <t>Resume progress tracker</t>
+      <c r="C18" s="10" t="inlineStr">
+        <is>
+          <t>Resume progress tracker [default: checkpoint.json]</t>
         </is>
       </c>
     </row>
@@ -4411,20 +5869,20 @@
           <t>errors.log</t>
         </is>
       </c>
-      <c r="C19" s="7" t="inlineStr">
-        <is>
-          <t>Error log file</t>
+      <c r="C19" s="10" t="inlineStr">
+        <is>
+          <t>Error log file [default: errors.log]</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="inlineStr">
+      <c r="A20" s="8" t="inlineStr">
         <is>
           <t># Step 3 — Cross References</t>
         </is>
       </c>
-      <c r="B20" s="4" t="inlineStr"/>
-      <c r="C20" s="4" t="inlineStr"/>
+      <c r="B20" s="8" t="inlineStr"/>
+      <c r="C20" s="7" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -4437,9 +5895,9 @@
           <t>3 - cross_references</t>
         </is>
       </c>
-      <c r="C21" s="7" t="inlineStr">
-        <is>
-          <t>Sub-folder name</t>
+      <c r="C21" s="10" t="inlineStr">
+        <is>
+          <t>Sub-folder name [default: 3 - cross_references]</t>
         </is>
       </c>
     </row>
@@ -4454,20 +5912,20 @@
           <t>cross_references.csv</t>
         </is>
       </c>
-      <c r="C22" s="7" t="inlineStr">
-        <is>
-          <t>CSV output</t>
+      <c r="C22" s="10" t="inlineStr">
+        <is>
+          <t>CSV output [default: cross_references.csv]</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="4" t="inlineStr">
+      <c r="A23" s="8" t="inlineStr">
         <is>
           <t># Step 4 — Heading Fixes</t>
         </is>
       </c>
-      <c r="B23" s="4" t="inlineStr"/>
-      <c r="C23" s="4" t="inlineStr"/>
+      <c r="B23" s="8" t="inlineStr"/>
+      <c r="C23" s="7" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -4480,9 +5938,9 @@
           <t>4 - heading_fixes</t>
         </is>
       </c>
-      <c r="C24" s="7" t="inlineStr">
-        <is>
-          <t>Sub-folder name</t>
+      <c r="C24" s="10" t="inlineStr">
+        <is>
+          <t>Sub-folder name [default: 4 - heading_fixes]</t>
         </is>
       </c>
     </row>
@@ -4497,20 +5955,20 @@
           <t>heading_changes.csv</t>
         </is>
       </c>
-      <c r="C25" s="7" t="inlineStr">
-        <is>
-          <t>Changes log CSV</t>
+      <c r="C25" s="10" t="inlineStr">
+        <is>
+          <t>Changes log CSV [default: heading_changes.csv]</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="4" t="inlineStr">
+      <c r="A26" s="8" t="inlineStr">
         <is>
           <t># Step 5 — Split Documents</t>
         </is>
       </c>
-      <c r="B26" s="4" t="inlineStr"/>
-      <c r="C26" s="4" t="inlineStr"/>
+      <c r="B26" s="8" t="inlineStr"/>
+      <c r="C26" s="7" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -4523,9 +5981,9 @@
           <t>5 - split_documents</t>
         </is>
       </c>
-      <c r="C27" s="7" t="inlineStr">
-        <is>
-          <t>Sub-folder name</t>
+      <c r="C27" s="10" t="inlineStr">
+        <is>
+          <t>Sub-folder name [default: 5 - split_documents]</t>
         </is>
       </c>
     </row>
@@ -4540,20 +5998,20 @@
           <t>split_manifest.csv</t>
         </is>
       </c>
-      <c r="C28" s="7" t="inlineStr">
-        <is>
-          <t>Split manifest CSV</t>
+      <c r="C28" s="10" t="inlineStr">
+        <is>
+          <t>Split manifest CSV [default: split_manifest.csv]</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="4" t="inlineStr">
+      <c r="A29" s="8" t="inlineStr">
         <is>
           <t># Step 6 — Metadata</t>
         </is>
       </c>
-      <c r="B29" s="4" t="inlineStr"/>
-      <c r="C29" s="4" t="inlineStr"/>
+      <c r="B29" s="8" t="inlineStr"/>
+      <c r="C29" s="7" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -4566,9 +6024,9 @@
           <t>6 - metadata</t>
         </is>
       </c>
-      <c r="C30" s="7" t="inlineStr">
-        <is>
-          <t>Sub-folder name</t>
+      <c r="C30" s="10" t="inlineStr">
+        <is>
+          <t>Sub-folder name [default: 6 - metadata]</t>
         </is>
       </c>
     </row>
@@ -4583,20 +6041,20 @@
           <t>metadata_manifest.csv</t>
         </is>
       </c>
-      <c r="C31" s="7" t="inlineStr">
-        <is>
-          <t>Metadata manifest CSV</t>
+      <c r="C31" s="10" t="inlineStr">
+        <is>
+          <t>Metadata manifest CSV [default: metadata_manifest.csv]</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="4" t="inlineStr">
+      <c r="A32" s="8" t="inlineStr">
         <is>
           <t># Step 7 — Markdown</t>
         </is>
       </c>
-      <c r="B32" s="4" t="inlineStr"/>
-      <c r="C32" s="4" t="inlineStr"/>
+      <c r="B32" s="8" t="inlineStr"/>
+      <c r="C32" s="7" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -4609,20 +6067,20 @@
           <t>7 - markdown</t>
         </is>
       </c>
-      <c r="C33" s="7" t="inlineStr">
-        <is>
-          <t>Sub-folder name</t>
+      <c r="C33" s="10" t="inlineStr">
+        <is>
+          <t>Sub-folder name [default: 7 - markdown]</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="4" t="inlineStr">
+      <c r="A34" s="8" t="inlineStr">
         <is>
           <t># Step 8 — JSONL</t>
         </is>
       </c>
-      <c r="B34" s="4" t="inlineStr"/>
-      <c r="C34" s="4" t="inlineStr"/>
+      <c r="B34" s="8" t="inlineStr"/>
+      <c r="C34" s="7" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -4635,20 +6093,20 @@
           <t>8 - jsonl</t>
         </is>
       </c>
-      <c r="C35" s="7" t="inlineStr">
-        <is>
-          <t>Sub-folder name</t>
+      <c r="C35" s="10" t="inlineStr">
+        <is>
+          <t>Sub-folder name [default: 8 - jsonl]</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="4" t="inlineStr">
+      <c r="A36" s="8" t="inlineStr">
         <is>
           <t># Step 9 — Validation</t>
         </is>
       </c>
-      <c r="B36" s="4" t="inlineStr"/>
-      <c r="C36" s="4" t="inlineStr"/>
+      <c r="B36" s="8" t="inlineStr"/>
+      <c r="C36" s="7" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -4661,9 +6119,9 @@
           <t>9 - validation</t>
         </is>
       </c>
-      <c r="C37" s="7" t="inlineStr">
-        <is>
-          <t>Sub-folder name</t>
+      <c r="C37" s="10" t="inlineStr">
+        <is>
+          <t>Sub-folder name [default: 9 - validation]</t>
         </is>
       </c>
     </row>
@@ -4678,9 +6136,9 @@
           <t>control_validation.csv</t>
         </is>
       </c>
-      <c r="C38" s="7" t="inlineStr">
-        <is>
-          <t>CSV output</t>
+      <c r="C38" s="10" t="inlineStr">
+        <is>
+          <t>CSV output [default: control_validation.csv]</t>
         </is>
       </c>
     </row>
@@ -4695,20 +6153,20 @@
           <t>validation_review.xlsx</t>
         </is>
       </c>
-      <c r="C39" s="7" t="inlineStr">
-        <is>
-          <t>Human review workbook</t>
+      <c r="C39" s="10" t="inlineStr">
+        <is>
+          <t>Human review workbook [default: validation_review.xlsx]</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="4" t="inlineStr">
+      <c r="A40" s="8" t="inlineStr">
         <is>
           <t># Consolidated Report</t>
         </is>
       </c>
-      <c r="B40" s="4" t="inlineStr"/>
-      <c r="C40" s="4" t="inlineStr"/>
+      <c r="B40" s="8" t="inlineStr"/>
+      <c r="C40" s="7" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -4719,9 +6177,9 @@
       <c r="B41" t="b">
         <v>1</v>
       </c>
-      <c r="C41" s="7" t="inlineStr">
-        <is>
-          <t>Build single .xlsx workbook after all steps</t>
+      <c r="C41" s="10" t="inlineStr">
+        <is>
+          <t>Build single .xlsx workbook after all steps [default: TRUE]</t>
         </is>
       </c>
     </row>
@@ -4736,9 +6194,9 @@
           <t>DPS_Report</t>
         </is>
       </c>
-      <c r="C42" s="7" t="inlineStr">
-        <is>
-          <t>Prefix for timestamped filename</t>
+      <c r="C42" s="10" t="inlineStr">
+        <is>
+          <t>Prefix for timestamped filename [default: DPS_Report]</t>
         </is>
       </c>
     </row>
@@ -4768,30 +6226,30 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="6" t="inlineStr">
         <is>
           <t>Keyword</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="6" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="8" t="inlineStr">
         <is>
           <t># Purpose</t>
         </is>
       </c>
-      <c r="B2" s="4" t="inlineStr"/>
-      <c r="C2" s="3" t="inlineStr"/>
+      <c r="B2" s="8" t="inlineStr"/>
+      <c r="C2" s="7" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -4804,7 +6262,7 @@
           <t>purpose</t>
         </is>
       </c>
-      <c r="C3" s="6" t="inlineStr">
+      <c r="C3" s="10" t="inlineStr">
         <is>
           <t>Keywords the profiler matches against H1 headings to classify each section</t>
         </is>
@@ -4821,7 +6279,7 @@
           <t>policy purpose</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr"/>
+      <c r="C4" s="9" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -4834,7 +6292,7 @@
           <t>1.0 purpose</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr"/>
+      <c r="C5" s="9" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -4847,16 +6305,16 @@
           <t>document purpose</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr"/>
+      <c r="C6" s="9" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t># Scope</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr"/>
-      <c r="C7" s="3" t="inlineStr"/>
+      <c r="B7" s="8" t="inlineStr"/>
+      <c r="C7" s="7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -4869,7 +6327,7 @@
           <t>scope</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr"/>
+      <c r="C8" s="10" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -4882,7 +6340,7 @@
           <t>policy scope</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr"/>
+      <c r="C9" s="9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -4895,7 +6353,7 @@
           <t>2.0 scope</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr"/>
+      <c r="C10" s="9" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -4908,7 +6366,7 @@
           <t>applicability</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr"/>
+      <c r="C11" s="9" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -4921,16 +6379,16 @@
           <t>applicability and scope</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr"/>
+      <c r="C12" s="9" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="A13" s="8" t="inlineStr">
         <is>
           <t># Intent</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr"/>
-      <c r="C13" s="3" t="inlineStr"/>
+      <c r="B13" s="8" t="inlineStr"/>
+      <c r="C13" s="7" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -4943,7 +6401,7 @@
           <t>intent</t>
         </is>
       </c>
-      <c r="C14" s="6" t="inlineStr"/>
+      <c r="C14" s="10" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -4956,7 +6414,7 @@
           <t>policy intent</t>
         </is>
       </c>
-      <c r="C15" s="5" t="inlineStr"/>
+      <c r="C15" s="9" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -4969,7 +6427,7 @@
           <t>3.0 intent</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr"/>
+      <c r="C16" s="9" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -4982,7 +6440,7 @@
           <t>objective</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr"/>
+      <c r="C17" s="9" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -4995,7 +6453,7 @@
           <t>policy objective</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr"/>
+      <c r="C18" s="9" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -5008,16 +6466,16 @@
           <t>security objective</t>
         </is>
       </c>
-      <c r="C19" s="5" t="inlineStr"/>
+      <c r="C19" s="9" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="inlineStr">
+      <c r="A20" s="8" t="inlineStr">
         <is>
           <t># Controls</t>
         </is>
       </c>
-      <c r="B20" s="4" t="inlineStr"/>
-      <c r="C20" s="3" t="inlineStr"/>
+      <c r="B20" s="8" t="inlineStr"/>
+      <c r="C20" s="7" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -5030,7 +6488,7 @@
           <t>controls</t>
         </is>
       </c>
-      <c r="C21" s="6" t="inlineStr"/>
+      <c r="C21" s="10" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -5043,7 +6501,7 @@
           <t>technical controls</t>
         </is>
       </c>
-      <c r="C22" s="5" t="inlineStr"/>
+      <c r="C22" s="9" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -5056,7 +6514,7 @@
           <t>security controls</t>
         </is>
       </c>
-      <c r="C23" s="5" t="inlineStr"/>
+      <c r="C23" s="9" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -5069,7 +6527,7 @@
           <t>4.0 controls</t>
         </is>
       </c>
-      <c r="C24" s="5" t="inlineStr"/>
+      <c r="C24" s="9" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -5082,7 +6540,7 @@
           <t>control requirements</t>
         </is>
       </c>
-      <c r="C25" s="5" t="inlineStr"/>
+      <c r="C25" s="9" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -5095,7 +6553,7 @@
           <t>requirements</t>
         </is>
       </c>
-      <c r="C26" s="5" t="inlineStr"/>
+      <c r="C26" s="9" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -5108,7 +6566,7 @@
           <t>policy requirements</t>
         </is>
       </c>
-      <c r="C27" s="5" t="inlineStr"/>
+      <c r="C27" s="9" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -5121,16 +6579,16 @@
           <t>implementation requirements</t>
         </is>
       </c>
-      <c r="C28" s="5" t="inlineStr"/>
+      <c r="C28" s="9" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="4" t="inlineStr">
+      <c r="A29" s="8" t="inlineStr">
         <is>
           <t># Appendix</t>
         </is>
       </c>
-      <c r="B29" s="4" t="inlineStr"/>
-      <c r="C29" s="3" t="inlineStr"/>
+      <c r="B29" s="8" t="inlineStr"/>
+      <c r="C29" s="7" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -5143,7 +6601,7 @@
           <t>appendix</t>
         </is>
       </c>
-      <c r="C30" s="6" t="inlineStr"/>
+      <c r="C30" s="10" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -5156,7 +6614,7 @@
           <t>appendices</t>
         </is>
       </c>
-      <c r="C31" s="5" t="inlineStr"/>
+      <c r="C31" s="9" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -5169,7 +6627,7 @@
           <t>5.0 appendix</t>
         </is>
       </c>
-      <c r="C32" s="5" t="inlineStr"/>
+      <c r="C32" s="9" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -5182,7 +6640,7 @@
           <t>supplementary</t>
         </is>
       </c>
-      <c r="C33" s="5" t="inlineStr"/>
+      <c r="C33" s="9" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -5195,7 +6653,7 @@
           <t>reference</t>
         </is>
       </c>
-      <c r="C34" s="5" t="inlineStr"/>
+      <c r="C34" s="9" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -5208,7 +6666,7 @@
           <t>references</t>
         </is>
       </c>
-      <c r="C35" s="5" t="inlineStr"/>
+      <c r="C35" s="9" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -5221,7 +6679,7 @@
           <t>glossary</t>
         </is>
       </c>
-      <c r="C36" s="5" t="inlineStr"/>
+      <c r="C36" s="9" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -5234,7 +6692,7 @@
           <t>definitions</t>
         </is>
       </c>
-      <c r="C37" s="5" t="inlineStr"/>
+      <c r="C37" s="9" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:C37"/>
@@ -5257,186 +6715,186 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>Setting</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="6" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="6" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t># Built-in Heading Styles</t>
         </is>
       </c>
-      <c r="B2" s="4" t="inlineStr"/>
-      <c r="C2" s="3" t="inlineStr"/>
+      <c r="B2" s="8" t="inlineStr"/>
+      <c r="C2" s="7" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="inlineStr">
-        <is>
-          <t>## Standard Word heading style names (list below)</t>
+      <c r="A3" s="10" t="inlineStr">
+        <is>
+          <t>## Column A = style name (one per row). Standard Word heading style names</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
-      <c r="C3" s="5" t="inlineStr"/>
+      <c r="C3" s="9" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" s="9" t="inlineStr">
         <is>
           <t>Heading 1</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
-      <c r="C4" s="5" t="inlineStr"/>
+      <c r="C4" s="9" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" s="9" t="inlineStr">
         <is>
           <t>Heading 2</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
-      <c r="C5" s="5" t="inlineStr"/>
+      <c r="C5" s="9" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="A6" s="9" t="inlineStr">
         <is>
           <t>Heading 3</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
-      <c r="C6" s="5" t="inlineStr"/>
+      <c r="C6" s="9" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" s="9" t="inlineStr">
         <is>
           <t>Heading 4</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
-      <c r="C7" s="5" t="inlineStr"/>
+      <c r="C7" s="9" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="A8" s="9" t="inlineStr">
         <is>
           <t>heading 1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
-      <c r="C8" s="5" t="inlineStr"/>
+      <c r="C8" s="9" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="A9" s="9" t="inlineStr">
         <is>
           <t>heading 2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
-      <c r="C9" s="5" t="inlineStr"/>
+      <c r="C9" s="9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="A10" s="9" t="inlineStr">
         <is>
           <t>heading 3</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
-      <c r="C10" s="5" t="inlineStr"/>
+      <c r="C10" s="9" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="A11" s="9" t="inlineStr">
         <is>
           <t>heading 4</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
-      <c r="C11" s="5" t="inlineStr"/>
+      <c r="C11" s="9" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="A12" s="7" t="inlineStr">
         <is>
           <t># Custom Heading Styles</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr"/>
-      <c r="C12" s="3" t="inlineStr"/>
+      <c r="B12" s="8" t="inlineStr"/>
+      <c r="C12" s="7" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="6" t="inlineStr">
-        <is>
-          <t>## Your org's custom Word heading style names (list below)</t>
+      <c r="A13" s="10" t="inlineStr">
+        <is>
+          <t>## Column A = style name (one per row). Your org's custom heading style names</t>
         </is>
       </c>
       <c r="B13" t="inlineStr"/>
-      <c r="C13" s="5" t="inlineStr"/>
+      <c r="C13" s="9" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="inlineStr">
+      <c r="A14" s="9" t="inlineStr">
         <is>
           <t>Policy Heading 1</t>
         </is>
       </c>
       <c r="B14" t="inlineStr"/>
-      <c r="C14" s="5" t="inlineStr"/>
+      <c r="C14" s="9" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="A15" s="9" t="inlineStr">
         <is>
           <t>Policy Heading 2</t>
         </is>
       </c>
       <c r="B15" t="inlineStr"/>
-      <c r="C15" s="5" t="inlineStr"/>
+      <c r="C15" s="9" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="inlineStr">
+      <c r="A16" s="9" t="inlineStr">
         <is>
           <t>TOC Heading</t>
         </is>
       </c>
       <c r="B16" t="inlineStr"/>
-      <c r="C16" s="5" t="inlineStr"/>
+      <c r="C16" s="9" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="inlineStr">
+      <c r="A17" s="9" t="inlineStr">
         <is>
           <t>AppendixHeading</t>
         </is>
       </c>
       <c r="B17" t="inlineStr"/>
-      <c r="C17" s="5" t="inlineStr"/>
+      <c r="C17" s="9" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="inlineStr">
+      <c r="A18" s="7" t="inlineStr">
         <is>
           <t># Custom Style Map</t>
         </is>
       </c>
-      <c r="B18" s="4" t="inlineStr"/>
-      <c r="C18" s="3" t="inlineStr"/>
+      <c r="B18" s="8" t="inlineStr"/>
+      <c r="C18" s="7" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="6" t="inlineStr">
-        <is>
-          <t>## Maps your org's custom styles to standard Heading 1/2/3 (Key → Value)</t>
+      <c r="A19" s="10" t="inlineStr">
+        <is>
+          <t>## Column A = custom style name, Column B = standard heading it maps to</t>
         </is>
       </c>
       <c r="B19" t="inlineStr"/>
-      <c r="C19" s="5" t="inlineStr"/>
+      <c r="C19" s="9" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="5" t="inlineStr">
+      <c r="A20" s="9" t="inlineStr">
         <is>
           <t>policy heading 1</t>
         </is>
@@ -5446,10 +6904,10 @@
           <t>Heading 1</t>
         </is>
       </c>
-      <c r="C20" s="5" t="inlineStr"/>
+      <c r="C20" s="9" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="inlineStr">
+      <c r="A21" s="9" t="inlineStr">
         <is>
           <t>policy heading 2</t>
         </is>
@@ -5459,10 +6917,10 @@
           <t>Heading 2</t>
         </is>
       </c>
-      <c r="C21" s="5" t="inlineStr"/>
+      <c r="C21" s="9" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="5" t="inlineStr">
+      <c r="A22" s="9" t="inlineStr">
         <is>
           <t>policy heading 3</t>
         </is>
@@ -5472,10 +6930,10 @@
           <t>Heading 3</t>
         </is>
       </c>
-      <c r="C22" s="5" t="inlineStr"/>
+      <c r="C22" s="9" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="5" t="inlineStr">
+      <c r="A23" s="9" t="inlineStr">
         <is>
           <t>policyheading1</t>
         </is>
@@ -5485,10 +6943,10 @@
           <t>Heading 1</t>
         </is>
       </c>
-      <c r="C23" s="5" t="inlineStr"/>
+      <c r="C23" s="9" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="5" t="inlineStr">
+      <c r="A24" s="9" t="inlineStr">
         <is>
           <t>policyheading2</t>
         </is>
@@ -5498,10 +6956,10 @@
           <t>Heading 2</t>
         </is>
       </c>
-      <c r="C24" s="5" t="inlineStr"/>
+      <c r="C24" s="9" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="inlineStr">
+      <c r="A25" s="9" t="inlineStr">
         <is>
           <t>policyheading3</t>
         </is>
@@ -5511,10 +6969,10 @@
           <t>Heading 3</t>
         </is>
       </c>
-      <c r="C25" s="5" t="inlineStr"/>
+      <c r="C25" s="9" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="5" t="inlineStr">
+      <c r="A26" s="9" t="inlineStr">
         <is>
           <t>doc heading 1</t>
         </is>
@@ -5524,10 +6982,10 @@
           <t>Heading 1</t>
         </is>
       </c>
-      <c r="C26" s="5" t="inlineStr"/>
+      <c r="C26" s="9" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="5" t="inlineStr">
+      <c r="A27" s="9" t="inlineStr">
         <is>
           <t>doc heading 2</t>
         </is>
@@ -5537,10 +6995,10 @@
           <t>Heading 2</t>
         </is>
       </c>
-      <c r="C27" s="5" t="inlineStr"/>
+      <c r="C27" s="9" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="5" t="inlineStr">
+      <c r="A28" s="9" t="inlineStr">
         <is>
           <t>doc heading 3</t>
         </is>
@@ -5550,10 +7008,10 @@
           <t>Heading 3</t>
         </is>
       </c>
-      <c r="C28" s="5" t="inlineStr"/>
+      <c r="C28" s="9" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="5" t="inlineStr">
+      <c r="A29" s="9" t="inlineStr">
         <is>
           <t>heading1</t>
         </is>
@@ -5563,10 +7021,10 @@
           <t>Heading 1</t>
         </is>
       </c>
-      <c r="C29" s="5" t="inlineStr"/>
+      <c r="C29" s="9" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="5" t="inlineStr">
+      <c r="A30" s="9" t="inlineStr">
         <is>
           <t>heading2</t>
         </is>
@@ -5576,10 +7034,10 @@
           <t>Heading 2</t>
         </is>
       </c>
-      <c r="C30" s="5" t="inlineStr"/>
+      <c r="C30" s="9" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="5" t="inlineStr">
+      <c r="A31" s="9" t="inlineStr">
         <is>
           <t>heading3</t>
         </is>
@@ -5589,10 +7047,10 @@
           <t>Heading 3</t>
         </is>
       </c>
-      <c r="C31" s="5" t="inlineStr"/>
+      <c r="C31" s="9" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="5" t="inlineStr">
+      <c r="A32" s="9" t="inlineStr">
         <is>
           <t>title heading</t>
         </is>
@@ -5602,10 +7060,10 @@
           <t>Heading 1</t>
         </is>
       </c>
-      <c r="C32" s="5" t="inlineStr"/>
+      <c r="C32" s="9" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="5" t="inlineStr">
+      <c r="A33" s="9" t="inlineStr">
         <is>
           <t>section heading</t>
         </is>
@@ -5615,10 +7073,10 @@
           <t>Heading 1</t>
         </is>
       </c>
-      <c r="C33" s="5" t="inlineStr"/>
+      <c r="C33" s="9" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="5" t="inlineStr">
+      <c r="A34" s="9" t="inlineStr">
         <is>
           <t>subsection heading</t>
         </is>
@@ -5628,19 +7086,19 @@
           <t>Heading 2</t>
         </is>
       </c>
-      <c r="C34" s="5" t="inlineStr"/>
+      <c r="C34" s="9" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="3" t="inlineStr">
+      <c r="A35" s="7" t="inlineStr">
         <is>
           <t># Fake Heading Detection</t>
         </is>
       </c>
-      <c r="B35" s="4" t="inlineStr"/>
-      <c r="C35" s="3" t="inlineStr"/>
+      <c r="B35" s="8" t="inlineStr"/>
+      <c r="C35" s="7" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="5" t="inlineStr">
+      <c r="A36" s="9" t="inlineStr">
         <is>
           <t>fake_heading_min_font_size</t>
         </is>
@@ -5648,14 +7106,14 @@
       <c r="B36" t="n">
         <v>12</v>
       </c>
-      <c r="C36" s="6" t="inlineStr">
-        <is>
-          <t>Min font size (pt) for bold text to be a fake heading. Lower=more detected</t>
+      <c r="C36" s="10" t="inlineStr">
+        <is>
+          <t>Min font size (pt) for bold text to be a fake heading. Lower=more detected [default: 12]</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="5" t="inlineStr">
+      <c r="A37" s="9" t="inlineStr">
         <is>
           <t>fake_heading_max_chars</t>
         </is>
@@ -5663,14 +7121,14 @@
       <c r="B37" t="n">
         <v>200</v>
       </c>
-      <c r="C37" s="6" t="inlineStr">
-        <is>
-          <t>Max char length for profiler fake heading candidates</t>
+      <c r="C37" s="10" t="inlineStr">
+        <is>
+          <t>Max char length for profiler fake heading candidates [default: 200]</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="5" t="inlineStr">
+      <c r="A38" s="9" t="inlineStr">
         <is>
           <t>fake_heading_max_chars_fixer</t>
         </is>
@@ -5678,23 +7136,23 @@
       <c r="B38" t="n">
         <v>120</v>
       </c>
-      <c r="C38" s="6" t="inlineStr">
-        <is>
-          <t>Tighter limit for heading fixer (Step 3) conversion</t>
+      <c r="C38" s="10" t="inlineStr">
+        <is>
+          <t>Tighter limit for heading fixer (Step 4) conversion [default: 120]</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="3" t="inlineStr">
+      <c r="A39" s="7" t="inlineStr">
         <is>
           <t># Heading Level Patterns (Regex)</t>
         </is>
       </c>
-      <c r="B39" s="4" t="inlineStr"/>
-      <c r="C39" s="3" t="inlineStr"/>
+      <c r="B39" s="8" t="inlineStr"/>
+      <c r="C39" s="7" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="5" t="inlineStr">
+      <c r="A40" s="9" t="inlineStr">
         <is>
           <t>heading1_pattern</t>
         </is>
@@ -5704,14 +7162,14 @@
           <t>^(?:\d+\.0\s+|[IVXLC]+\.\s+)</t>
         </is>
       </c>
-      <c r="C40" s="6" t="inlineStr">
+      <c r="C40" s="10" t="inlineStr">
         <is>
           <t>Matches H1 numbering, e.g. "1.0 Purpose", "IV. Controls"</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="5" t="inlineStr">
+      <c r="A41" s="9" t="inlineStr">
         <is>
           <t>heading2_pattern</t>
         </is>
@@ -5721,14 +7179,14 @@
           <t>^(?:\d+\.\d+\s+|[A-Z]\.\s+)</t>
         </is>
       </c>
-      <c r="C41" s="6" t="inlineStr">
+      <c r="C41" s="10" t="inlineStr">
         <is>
           <t>Matches H2 numbering, e.g. "1.1 Access", "A. Overview"</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="5" t="inlineStr">
+      <c r="A42" s="9" t="inlineStr">
         <is>
           <t>heading3_pattern</t>
         </is>
@@ -5738,14 +7196,14 @@
           <t>^\d+\.\d+\.\d+\s+</t>
         </is>
       </c>
-      <c r="C42" s="6" t="inlineStr">
+      <c r="C42" s="10" t="inlineStr">
         <is>
           <t>Matches H3 numbering, e.g. "1.1.1 Sub-section"</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="5" t="inlineStr">
+      <c r="A43" s="9" t="inlineStr">
         <is>
           <t>default_heading_level</t>
         </is>
@@ -5753,9 +7211,9 @@
       <c r="B43" t="n">
         <v>2</v>
       </c>
-      <c r="C43" s="6" t="inlineStr">
-        <is>
-          <t>Default level when no numbering pattern matches (1 or 2)</t>
+      <c r="C43" s="10" t="inlineStr">
+        <is>
+          <t>Default level when no numbering pattern matches (1 or 2) [default: 2]</t>
         </is>
       </c>
     </row>
@@ -5780,33 +7238,33 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>Setting</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="6" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="6" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t># Settings</t>
         </is>
       </c>
-      <c r="B2" s="4" t="inlineStr"/>
-      <c r="C2" s="3" t="inlineStr"/>
+      <c r="B2" s="8" t="inlineStr"/>
+      <c r="C2" s="7" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" s="9" t="inlineStr">
         <is>
           <t>enabled</t>
         </is>
@@ -5814,14 +7272,14 @@
       <c r="B3" t="b">
         <v>0</v>
       </c>
-      <c r="C3" s="6" t="inlineStr">
-        <is>
-          <t>Set TRUE to activate text deletion during Step 3</t>
+      <c r="C3" s="10" t="inlineStr">
+        <is>
+          <t>Set TRUE to activate text deletion during Step 4 [default: FALSE]</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" s="9" t="inlineStr">
         <is>
           <t>case_sensitive</t>
         </is>
@@ -5829,107 +7287,107 @@
       <c r="B4" t="b">
         <v>1</v>
       </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>TRUE for exact case match, FALSE for case-insensitive</t>
+      <c r="C4" s="10" t="inlineStr">
+        <is>
+          <t>TRUE for exact case match, FALSE for case-insensitive [default: TRUE]</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t># Phrases to Delete</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr"/>
-      <c r="C5" s="3" t="inlineStr"/>
+      <c r="B5" s="8" t="inlineStr"/>
+      <c r="C5" s="7" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="10" t="inlineStr">
         <is>
           <t>## Add exact phrases to delete (one per row in column A). Originals are never modified.</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
-      <c r="C6" s="5" t="inlineStr"/>
+      <c r="C6" s="9" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="7" t="inlineStr">
         <is>
           <t># Sections to Delete</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr"/>
-      <c r="C7" s="3" t="inlineStr"/>
+      <c r="B7" s="8" t="inlineStr"/>
+      <c r="C7" s="7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="A8" s="10" t="inlineStr">
         <is>
           <t>## Delete an entire section: heading + all content until the next heading of same or higher level.</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
-      <c r="C8" s="5" t="inlineStr"/>
+      <c r="C8" s="9" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="6" t="inlineStr">
+      <c r="A9" s="10" t="inlineStr">
         <is>
           <t>## Match is case-insensitive substring on the heading text. Originals are never modified.</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
-      <c r="C9" s="5" t="inlineStr"/>
+      <c r="C9" s="9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr">
+      <c r="A10" s="10" t="inlineStr">
         <is>
           <t>## Example: 'Appendix A' deletes the Appendix A heading and everything below it until the next H1/H2.</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
-      <c r="C10" s="5" t="inlineStr"/>
+      <c r="C10" s="9" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" s="7" t="inlineStr">
         <is>
           <t>Section Heading</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B11" s="8" t="inlineStr">
         <is>
           <t>Delete (TRUE/FALSE)</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C11" s="7" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="inlineStr"/>
+      <c r="A12" s="9" t="inlineStr"/>
       <c r="B12" t="inlineStr"/>
-      <c r="C12" s="5" t="inlineStr"/>
+      <c r="C12" s="9" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="inlineStr"/>
+      <c r="A13" s="9" t="inlineStr"/>
       <c r="B13" t="inlineStr"/>
-      <c r="C13" s="5" t="inlineStr"/>
+      <c r="C13" s="9" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="inlineStr"/>
+      <c r="A14" s="9" t="inlineStr"/>
       <c r="B14" t="inlineStr"/>
-      <c r="C14" s="5" t="inlineStr"/>
+      <c r="C14" s="9" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr"/>
+      <c r="A15" s="9" t="inlineStr"/>
       <c r="B15" t="inlineStr"/>
-      <c r="C15" s="5" t="inlineStr"/>
+      <c r="C15" s="9" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="inlineStr"/>
+      <c r="A16" s="9" t="inlineStr"/>
       <c r="B16" t="inlineStr"/>
-      <c r="C16" s="5" t="inlineStr"/>
+      <c r="C16" s="9" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:C16"/>
@@ -5963,33 +7421,33 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>Setting</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="6" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="6" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t># Detection Settings</t>
         </is>
       </c>
-      <c r="B2" s="4" t="inlineStr"/>
-      <c r="C2" s="3" t="inlineStr"/>
+      <c r="B2" s="8" t="inlineStr"/>
+      <c r="C2" s="7" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" s="9" t="inlineStr">
         <is>
           <t>detect_hyperlink_crossrefs</t>
         </is>
@@ -5997,14 +7455,14 @@
       <c r="B3" t="b">
         <v>1</v>
       </c>
-      <c r="C3" s="6" t="inlineStr">
-        <is>
-          <t>Detect hyperlinks whose text looks like a section/policy ref</t>
+      <c r="C3" s="10" t="inlineStr">
+        <is>
+          <t>Detect hyperlinks whose text looks like a section/policy ref [default: TRUE]</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" s="9" t="inlineStr">
         <is>
           <t>detect_urls</t>
         </is>
@@ -6012,140 +7470,140 @@
       <c r="B4" t="b">
         <v>1</v>
       </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>Extract URLs from hyperlinks and bare text</t>
+      <c r="C4" s="10" t="inlineStr">
+        <is>
+          <t>Extract URLs from hyperlinks and bare text [default: TRUE]</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t># Profiler Patterns (Regex — Step 0)</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr"/>
-      <c r="C5" s="3" t="inlineStr"/>
+      <c r="B5" s="8" t="inlineStr"/>
+      <c r="C5" s="7" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="10" t="inlineStr">
         <is>
           <t>## Regex patterns for COUNTING cross-references in profiler</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
-      <c r="C6" s="5" t="inlineStr"/>
+      <c r="C6" s="9" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" s="9" t="inlineStr">
         <is>
           <t>see section\s+[\d\.]+[a-z]?</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
-      <c r="C7" s="5" t="inlineStr"/>
+      <c r="C7" s="9" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="A8" s="9" t="inlineStr">
         <is>
           <t>refer to\s+(section|the)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
-      <c r="C8" s="5" t="inlineStr"/>
+      <c r="C8" s="9" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="A9" s="9" t="inlineStr">
         <is>
           <t>as described in\s+(the|section)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
-      <c r="C9" s="5" t="inlineStr"/>
+      <c r="C9" s="9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="A10" s="9" t="inlineStr">
         <is>
           <t>per section\s+[\d\.]+</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
-      <c r="C10" s="5" t="inlineStr"/>
+      <c r="C10" s="9" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="A11" s="9" t="inlineStr">
         <is>
           <t>in accordance with\s+(the|section)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
-      <c r="C11" s="5" t="inlineStr"/>
+      <c r="C11" s="9" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="inlineStr">
+      <c r="A12" s="9" t="inlineStr">
         <is>
           <t>as defined in\s+(the|section)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>
-      <c r="C12" s="5" t="inlineStr"/>
+      <c r="C12" s="9" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="inlineStr">
+      <c r="A13" s="9" t="inlineStr">
         <is>
           <t>as outlined in\s+(the|section)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr"/>
-      <c r="C13" s="5" t="inlineStr"/>
+      <c r="C13" s="9" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="inlineStr">
+      <c r="A14" s="9" t="inlineStr">
         <is>
           <t>per the organization'?s\s+\w+</t>
         </is>
       </c>
       <c r="B14" t="inlineStr"/>
-      <c r="C14" s="5" t="inlineStr"/>
+      <c r="C14" s="9" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="A15" s="9" t="inlineStr">
         <is>
           <t>see the\s+\w+\s+policy</t>
         </is>
       </c>
       <c r="B15" t="inlineStr"/>
-      <c r="C15" s="5" t="inlineStr"/>
+      <c r="C15" s="9" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="inlineStr">
+      <c r="A16" s="9" t="inlineStr">
         <is>
           <t>as specified in\s+(the|section)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr"/>
-      <c r="C16" s="5" t="inlineStr"/>
+      <c r="C16" s="9" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr">
+      <c r="A17" s="7" t="inlineStr">
         <is>
           <t># Extraction Patterns (Step 2)</t>
         </is>
       </c>
-      <c r="B17" s="4" t="inlineStr"/>
-      <c r="C17" s="3" t="inlineStr"/>
+      <c r="B17" s="8" t="inlineStr"/>
+      <c r="C17" s="7" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="6" t="inlineStr">
+      <c r="A18" s="10" t="inlineStr">
         <is>
           <t>## Phrase | Type (internal/external). Extractor auto-builds regex from phrase.</t>
         </is>
       </c>
       <c r="B18" t="inlineStr"/>
-      <c r="C18" s="5" t="inlineStr"/>
+      <c r="C18" s="9" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="inlineStr">
+      <c r="A19" s="9" t="inlineStr">
         <is>
           <t>see</t>
         </is>
@@ -6155,10 +7613,10 @@
           <t>internal</t>
         </is>
       </c>
-      <c r="C19" s="5" t="inlineStr"/>
+      <c r="C19" s="9" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="5" t="inlineStr">
+      <c r="A20" s="9" t="inlineStr">
         <is>
           <t>refer to</t>
         </is>
@@ -6168,10 +7626,10 @@
           <t>internal</t>
         </is>
       </c>
-      <c r="C20" s="5" t="inlineStr"/>
+      <c r="C20" s="9" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="inlineStr">
+      <c r="A21" s="9" t="inlineStr">
         <is>
           <t>per</t>
         </is>
@@ -6181,10 +7639,10 @@
           <t>internal</t>
         </is>
       </c>
-      <c r="C21" s="5" t="inlineStr"/>
+      <c r="C21" s="9" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="5" t="inlineStr">
+      <c r="A22" s="9" t="inlineStr">
         <is>
           <t>as described in</t>
         </is>
@@ -6194,10 +7652,10 @@
           <t>internal</t>
         </is>
       </c>
-      <c r="C22" s="5" t="inlineStr"/>
+      <c r="C22" s="9" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="5" t="inlineStr">
+      <c r="A23" s="9" t="inlineStr">
         <is>
           <t>as defined in</t>
         </is>
@@ -6207,10 +7665,10 @@
           <t>internal</t>
         </is>
       </c>
-      <c r="C23" s="5" t="inlineStr"/>
+      <c r="C23" s="9" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="5" t="inlineStr">
+      <c r="A24" s="9" t="inlineStr">
         <is>
           <t>as described in</t>
         </is>
@@ -6220,10 +7678,10 @@
           <t>external</t>
         </is>
       </c>
-      <c r="C24" s="5" t="inlineStr"/>
+      <c r="C24" s="9" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="inlineStr">
+      <c r="A25" s="9" t="inlineStr">
         <is>
           <t>as defined in</t>
         </is>
@@ -6233,10 +7691,10 @@
           <t>external</t>
         </is>
       </c>
-      <c r="C25" s="5" t="inlineStr"/>
+      <c r="C25" s="9" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="5" t="inlineStr">
+      <c r="A26" s="9" t="inlineStr">
         <is>
           <t>refer to</t>
         </is>
@@ -6246,10 +7704,10 @@
           <t>external</t>
         </is>
       </c>
-      <c r="C26" s="5" t="inlineStr"/>
+      <c r="C26" s="9" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="5" t="inlineStr">
+      <c r="A27" s="9" t="inlineStr">
         <is>
           <t>in accordance with</t>
         </is>
@@ -6259,106 +7717,106 @@
           <t>external</t>
         </is>
       </c>
-      <c r="C27" s="5" t="inlineStr"/>
+      <c r="C27" s="9" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="inlineStr">
+      <c r="A28" s="7" t="inlineStr">
         <is>
           <t># Document Name Keywords</t>
         </is>
       </c>
-      <c r="B28" s="4" t="inlineStr"/>
-      <c r="C28" s="3" t="inlineStr"/>
+      <c r="B28" s="8" t="inlineStr"/>
+      <c r="C28" s="7" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="6" t="inlineStr">
-        <is>
-          <t>## External patterns match doc names ending in these keywords</t>
+      <c r="A29" s="10" t="inlineStr">
+        <is>
+          <t>## Column A = keyword (one per row). External patterns match doc names ending in these</t>
         </is>
       </c>
       <c r="B29" t="inlineStr"/>
-      <c r="C29" s="5" t="inlineStr"/>
+      <c r="C29" s="9" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="5" t="inlineStr">
+      <c r="A30" s="9" t="inlineStr">
         <is>
           <t>Policy</t>
         </is>
       </c>
       <c r="B30" t="inlineStr"/>
-      <c r="C30" s="5" t="inlineStr"/>
+      <c r="C30" s="9" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="5" t="inlineStr">
+      <c r="A31" s="9" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
       </c>
       <c r="B31" t="inlineStr"/>
-      <c r="C31" s="5" t="inlineStr"/>
+      <c r="C31" s="9" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="5" t="inlineStr">
+      <c r="A32" s="9" t="inlineStr">
         <is>
           <t>Plan</t>
         </is>
       </c>
       <c r="B32" t="inlineStr"/>
-      <c r="C32" s="5" t="inlineStr"/>
+      <c r="C32" s="9" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="5" t="inlineStr">
+      <c r="A33" s="9" t="inlineStr">
         <is>
           <t>Procedure</t>
         </is>
       </c>
       <c r="B33" t="inlineStr"/>
-      <c r="C33" s="5" t="inlineStr"/>
+      <c r="C33" s="9" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="5" t="inlineStr">
+      <c r="A34" s="9" t="inlineStr">
         <is>
           <t>Guide</t>
         </is>
       </c>
       <c r="B34" t="inlineStr"/>
-      <c r="C34" s="5" t="inlineStr"/>
+      <c r="C34" s="9" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="5" t="inlineStr">
+      <c r="A35" s="9" t="inlineStr">
         <is>
           <t>Guideline</t>
         </is>
       </c>
       <c r="B35" t="inlineStr"/>
-      <c r="C35" s="5" t="inlineStr"/>
+      <c r="C35" s="9" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="5" t="inlineStr">
+      <c r="A36" s="9" t="inlineStr">
         <is>
           <t>Program</t>
         </is>
       </c>
       <c r="B36" t="inlineStr"/>
-      <c r="C36" s="5" t="inlineStr"/>
+      <c r="C36" s="9" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="5" t="inlineStr">
+      <c r="A37" s="9" t="inlineStr">
         <is>
           <t>Framework</t>
         </is>
       </c>
       <c r="B37" t="inlineStr"/>
-      <c r="C37" s="5" t="inlineStr"/>
+      <c r="C37" s="9" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="5" t="inlineStr">
+      <c r="A38" s="9" t="inlineStr">
         <is>
           <t>Charter</t>
         </is>
       </c>
       <c r="B38" t="inlineStr"/>
-      <c r="C38" s="5" t="inlineStr"/>
+      <c r="C38" s="9" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:C38"/>
@@ -6389,30 +7847,30 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>Table Type</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="6" t="inlineStr">
         <is>
           <t>Keyword</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="6" t="inlineStr">
         <is>
           <t>Min Columns</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="8" t="inlineStr">
         <is>
           <t># Control Matrix</t>
         </is>
       </c>
-      <c r="B2" s="4" t="inlineStr"/>
-      <c r="C2" s="4" t="inlineStr"/>
+      <c r="B2" s="8" t="inlineStr"/>
+      <c r="C2" s="8" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -6550,13 +8008,13 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" s="8" t="inlineStr">
         <is>
           <t># Applicability Table</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr"/>
-      <c r="C12" s="4" t="inlineStr"/>
+      <c r="B12" s="8" t="inlineStr"/>
+      <c r="C12" s="8" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -6679,13 +8137,13 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="inlineStr">
+      <c r="A21" s="8" t="inlineStr">
         <is>
           <t># Reference Table</t>
         </is>
       </c>
-      <c r="B21" s="4" t="inlineStr"/>
-      <c r="C21" s="4" t="inlineStr"/>
+      <c r="B21" s="8" t="inlineStr"/>
+      <c r="C21" s="8" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -6778,13 +8236,13 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="4" t="inlineStr">
+      <c r="A28" s="8" t="inlineStr">
         <is>
           <t># Crosswalk Table</t>
         </is>
       </c>
-      <c r="B28" s="4" t="inlineStr"/>
-      <c r="C28" s="4" t="inlineStr"/>
+      <c r="B28" s="8" t="inlineStr"/>
+      <c r="C28" s="8" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -6892,13 +8350,13 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="4" t="inlineStr">
+      <c r="A36" s="8" t="inlineStr">
         <is>
           <t># Role Responsibility</t>
         </is>
       </c>
-      <c r="B36" s="4" t="inlineStr"/>
-      <c r="C36" s="4" t="inlineStr"/>
+      <c r="B36" s="8" t="inlineStr"/>
+      <c r="C36" s="8" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -6990,39 +8448,39 @@
   <dimension ref="A1:C16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="65" customWidth="1" min="1" max="1"/>
     <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="39" customWidth="1" min="3" max="3"/>
+    <col width="53" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>Setting</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="6" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="6" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t># Type A — Table-Heavy</t>
         </is>
       </c>
-      <c r="B2" s="4" t="inlineStr"/>
-      <c r="C2" s="4" t="inlineStr"/>
+      <c r="B2" s="8" t="inlineStr"/>
+      <c r="C2" s="8" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="9" t="inlineStr">
         <is>
           <t>type_a.min_table_content_pct</t>
         </is>
@@ -7030,23 +8488,23 @@
       <c r="B3" t="n">
         <v>40</v>
       </c>
-      <c r="C3" s="7" t="inlineStr">
-        <is>
-          <t>&gt;X% of content in tables → Type A</t>
+      <c r="C3" s="11" t="inlineStr">
+        <is>
+          <t>&gt;X% of content in tables → Type A [default: 40]</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="7" t="inlineStr">
         <is>
           <t># Type B — Prose-Heavy</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr"/>
-      <c r="C4" s="4" t="inlineStr"/>
+      <c r="B4" s="8" t="inlineStr"/>
+      <c r="C4" s="8" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="9" t="inlineStr">
         <is>
           <t>type_b.max_table_content_pct</t>
         </is>
@@ -7054,32 +8512,32 @@
       <c r="B5" t="n">
         <v>10</v>
       </c>
-      <c r="C5" s="7" t="inlineStr">
-        <is>
-          <t>&lt;X% of content in tables → Type B</t>
+      <c r="C5" s="11" t="inlineStr">
+        <is>
+          <t>&lt;X% of content in tables → Type B [default: 10]</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t># Type C — Hybrid (Procedure Keywords)</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr"/>
-      <c r="C6" s="4" t="inlineStr"/>
+      <c r="B6" s="8" t="inlineStr"/>
+      <c r="C6" s="8" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t># Keywords that signal embedded procedures</t>
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>## Column A = keyword (one per row). Keywords that signal embedded procedures</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
-      <c r="C7" s="7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="9" t="inlineStr">
         <is>
           <t>step 1</t>
         </is>
@@ -7088,7 +8546,7 @@
       <c r="C8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="9" t="inlineStr">
         <is>
           <t>step 2</t>
         </is>
@@ -7097,7 +8555,7 @@
       <c r="C9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="9" t="inlineStr">
         <is>
           <t>procedure</t>
         </is>
@@ -7106,7 +8564,7 @@
       <c r="C10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="9" t="inlineStr">
         <is>
           <t>escalation</t>
         </is>
@@ -7115,7 +8573,7 @@
       <c r="C11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="9" t="inlineStr">
         <is>
           <t>workflow</t>
         </is>
@@ -7124,7 +8582,7 @@
       <c r="C12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="9" t="inlineStr">
         <is>
           <t>response process</t>
         </is>
@@ -7133,7 +8591,7 @@
       <c r="C13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="9" t="inlineStr">
         <is>
           <t>playbook</t>
         </is>
@@ -7142,16 +8600,16 @@
       <c r="C14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="inlineStr">
+      <c r="A15" s="7" t="inlineStr">
         <is>
           <t># Type D — Appendix-Dominant</t>
         </is>
       </c>
-      <c r="B15" s="4" t="inlineStr"/>
-      <c r="C15" s="4" t="inlineStr"/>
+      <c r="B15" s="8" t="inlineStr"/>
+      <c r="C15" s="8" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="9" t="inlineStr">
         <is>
           <t>type_d.min_appendix_content_pct</t>
         </is>
@@ -7159,9 +8617,9 @@
       <c r="B16" t="n">
         <v>60</v>
       </c>
-      <c r="C16" s="7" t="inlineStr">
-        <is>
-          <t>&gt;X% of content in appendix → Type D</t>
+      <c r="C16" s="11" t="inlineStr">
+        <is>
+          <t>&gt;X% of content in appendix → Type D [default: 60]</t>
         </is>
       </c>
     </row>
